--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15AFF105-C8BE-4DBD-B2CB-C4DCFEC0837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED402383-1226-47BE-AB4B-30EEEA9FE3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -700,10 +700,15 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -714,7 +719,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -722,11 +727,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -738,6 +758,11 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1081,40 +1106,41 @@
     <col min="8" max="8" width="26.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="43.28515625" style="2" customWidth="1"/>
     <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="5" t="s">
         <v>2</v>
       </c>
     </row>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED402383-1226-47BE-AB4B-30EEEA9FE3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072A8053-0446-45B9-ADEF-8A8454A4FC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>Activity Name</t>
   </si>
   <si>
-    <t>Primary Constraint</t>
-  </si>
-  <si>
     <t>AR-FL-KD-1040</t>
   </si>
   <si>
@@ -687,10 +684,13 @@
     <t>Remaining Duration</t>
   </si>
   <si>
-    <t>Variance - BL Project Finish Date</t>
-  </si>
-  <si>
     <t>Total Float</t>
+  </si>
+  <si>
+    <t>Variance - BL1 Finish Date</t>
+  </si>
+  <si>
+    <t>Comments</t>
   </si>
 </sst>
 </file>
@@ -719,7 +719,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -727,26 +727,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -758,11 +743,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,1317 +1083,1318 @@
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
     <col min="2" max="2" width="54" style="1" customWidth="1"/>
-    <col min="3" max="7" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="43.28515625" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="3" max="5" width="20" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="43.28515625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="10" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="5" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H1" t="s">
         <v>216</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="E1" s="6" t="s">
+      <c r="I1" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" t="s">
         <v>218</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4">
+        <v>46161.708333333299</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="4">
-        <v>46171.708333333299</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="4">
-        <v>46161.708333333299</v>
+      <c r="H2" t="s">
+        <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J2" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="4">
+        <v>46164.333333333299</v>
+      </c>
+      <c r="D3" s="4">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="E3" s="4">
+        <v>46155.333333333299</v>
+      </c>
+      <c r="F3" s="4">
+        <v>46161.708333333299</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="4">
-        <v>46164.333333333299</v>
-      </c>
-      <c r="E3" s="4">
-        <v>46171.708333333299</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46155.333333333299</v>
-      </c>
-      <c r="H3" s="4">
-        <v>46161.708333333299</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" t="s">
-        <v>8</v>
+      <c r="J3" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <v>46163.708333333299</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4">
+        <v>46154.708333333299</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="4">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="4">
-        <v>46154.708333333299</v>
+      <c r="H4" t="s">
+        <v>7</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" t="s">
-        <v>8</v>
+        <v>4</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="4">
+        <v>46121.333333333299</v>
+      </c>
+      <c r="D5" s="4">
+        <v>46129.708333333299</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46107.333333333299</v>
+      </c>
+      <c r="F5" s="4">
+        <v>46119.708333333299</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="4">
-        <v>46121.333333333299</v>
-      </c>
-      <c r="E5" s="4">
-        <v>46129.708333333299</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="4">
-        <v>46107.333333333299</v>
-      </c>
-      <c r="H5" s="4">
-        <v>46119.708333333299</v>
+      <c r="H5" t="s">
+        <v>5</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
+      <c r="C6" s="4">
+        <v>46100.333333333299</v>
       </c>
       <c r="D6" s="4">
+        <v>46106.708333333299</v>
+      </c>
+      <c r="E6" s="4">
         <v>46100.333333333299</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>46106.708333333299</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46100.333333333299</v>
-      </c>
-      <c r="H6" s="4">
-        <v>46106.708333333299</v>
+      <c r="G6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J6" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
+      <c r="C7" s="4">
+        <v>46097.333333333299</v>
       </c>
       <c r="D7" s="4">
+        <v>46106.708333333299</v>
+      </c>
+      <c r="E7" s="4">
         <v>46097.333333333299</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>46106.708333333299</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46097.333333333299</v>
-      </c>
-      <c r="H7" s="4">
-        <v>46106.708333333299</v>
+      <c r="G7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J7" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="4">
         <v>46097.333333333299</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="E8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="4">
         <v>46097.333333333299</v>
       </c>
+      <c r="G8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J8" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
+      <c r="C9" s="4">
+        <v>46090.333333333299</v>
       </c>
       <c r="D9" s="4">
+        <v>46094.708333333299</v>
+      </c>
+      <c r="E9" s="4">
         <v>46090.333333333299</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <v>46094.708333333299</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="H9" s="4">
-        <v>46094.708333333299</v>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
+      <c r="C10" s="4">
+        <v>46090.333333333299</v>
       </c>
       <c r="D10" s="4">
+        <v>46094.708333333299</v>
+      </c>
+      <c r="E10" s="4">
         <v>46090.333333333299</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <v>46094.708333333299</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="4">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="H10" s="4">
-        <v>46094.708333333299</v>
+      <c r="G10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" s="4">
+        <v>46174.333333333299</v>
+      </c>
+      <c r="D11" s="4">
+        <v>46175.708333333299</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46139.333333333299</v>
+      </c>
+      <c r="F11" s="4">
+        <v>46140.708333333299</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="4">
-        <v>46174.333333333299</v>
-      </c>
-      <c r="E11" s="4">
-        <v>46175.708333333299</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46139.333333333299</v>
-      </c>
-      <c r="H11" s="4">
-        <v>46140.708333333299</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" t="s">
-        <v>32</v>
+      <c r="J11" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="4">
+        <v>46141.333333333299</v>
+      </c>
+      <c r="D12" s="4">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46132.333333333299</v>
+      </c>
+      <c r="F12" s="4">
+        <v>46136.708333333299</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="4">
-        <v>46141.333333333299</v>
-      </c>
-      <c r="E12" s="4">
-        <v>46171.708333333299</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46132.333333333299</v>
-      </c>
-      <c r="H12" s="4">
-        <v>46136.708333333299</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
+      <c r="J12" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
+      <c r="C13" s="4">
+        <v>46136.333333333299</v>
       </c>
       <c r="D13" s="4">
-        <v>46136.333333333299</v>
+        <v>46140.708333333299</v>
       </c>
       <c r="E13" s="4">
-        <v>46140.708333333299</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="4">
         <v>46127.333333333299</v>
       </c>
-      <c r="H13" s="4">
+      <c r="F13" s="4">
         <v>46129.708333333299</v>
       </c>
+      <c r="G13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H13" t="s">
+        <v>5</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" t="s">
         <v>38</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
+      <c r="C14" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D14" s="4">
-        <v>46129.333333333299</v>
+        <v>46135.708333333299</v>
       </c>
       <c r="E14" s="4">
-        <v>46135.708333333299</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="4">
         <v>46120.333333333299</v>
       </c>
-      <c r="H14" s="4">
+      <c r="F14" s="4">
         <v>46126.708333333299</v>
       </c>
+      <c r="G14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" t="s">
+        <v>5</v>
+      </c>
       <c r="I14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J14" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="4">
+        <v>46163.333333333299</v>
+      </c>
+      <c r="D15" s="4">
+        <v>46163.708333333299</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46154.333333333299</v>
+      </c>
+      <c r="F15" s="4">
+        <v>46154.708333333299</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="4">
-        <v>46163.333333333299</v>
-      </c>
-      <c r="E15" s="4">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46154.333333333299</v>
-      </c>
-      <c r="H15" s="4">
-        <v>46154.708333333299</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J15" t="s">
-        <v>8</v>
+      <c r="J15" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
+      <c r="C16" s="4">
+        <v>46162.333333333299</v>
       </c>
       <c r="D16" s="4">
-        <v>46162.333333333299</v>
+        <v>46169.708333333299</v>
       </c>
       <c r="E16" s="4">
-        <v>46169.708333333299</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="4">
         <v>46153.333333333299</v>
       </c>
-      <c r="H16" s="4">
+      <c r="F16" s="4">
         <v>46157.708333333299</v>
       </c>
+      <c r="G16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>39</v>
+      </c>
       <c r="I16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" t="s">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>11</v>
+      <c r="C17" s="4">
+        <v>46156.333333333299</v>
       </c>
       <c r="D17" s="4">
-        <v>46156.333333333299</v>
+        <v>46162.708333333299</v>
       </c>
       <c r="E17" s="4">
-        <v>46162.708333333299</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="4">
         <v>46147.333333333299</v>
       </c>
-      <c r="H17" s="4">
+      <c r="F17" s="4">
         <v>46153.708333333299</v>
       </c>
+      <c r="G17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>7</v>
+      </c>
       <c r="I17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="B18" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>11</v>
+      <c r="C18" s="4">
+        <v>46149.333333333299</v>
       </c>
       <c r="D18" s="4">
-        <v>46149.333333333299</v>
+        <v>46155.708333333299</v>
       </c>
       <c r="E18" s="4">
-        <v>46155.708333333299</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="4">
         <v>46139.333333333299</v>
       </c>
-      <c r="H18" s="4">
+      <c r="F18" s="4">
         <v>46143.708333333299</v>
       </c>
+      <c r="G18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" t="s">
+        <v>7</v>
+      </c>
       <c r="I18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" t="s">
-        <v>8</v>
+        <v>10</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" t="s">
         <v>50</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" s="4">
+        <v>46141.333333333299</v>
+      </c>
+      <c r="D19" s="4">
+        <v>46148.708333333299</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46132.333333333299</v>
+      </c>
+      <c r="F19" s="4">
+        <v>46136.708333333299</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
+        <v>7</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="4">
-        <v>46141.333333333299</v>
-      </c>
-      <c r="E19" s="4">
-        <v>46148.708333333299</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46132.333333333299</v>
-      </c>
-      <c r="H19" s="4">
-        <v>46136.708333333299</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" t="s">
-        <v>8</v>
-      </c>
       <c r="K19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
         <v>53</v>
       </c>
-      <c r="B20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>5</v>
+      <c r="C20" s="4">
+        <v>46129.333333333299</v>
       </c>
       <c r="D20" s="4">
-        <v>46129.333333333299</v>
+        <v>46132.708333333299</v>
       </c>
       <c r="E20" s="4">
-        <v>46132.708333333299</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="4">
         <v>46120.333333333299</v>
       </c>
-      <c r="H20" s="4">
+      <c r="F20" s="4">
         <v>46121.708333333299</v>
       </c>
+      <c r="G20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H20" t="s">
+        <v>5</v>
+      </c>
       <c r="I20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J20" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
         <v>55</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="D21" s="4">
+        <v>45953.708333333299</v>
+      </c>
+      <c r="E21" s="4">
+        <v>45947.333333333299</v>
+      </c>
+      <c r="F21" s="4">
+        <v>45953.708333333299</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K21" t="s">
         <v>56</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="4">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E21" s="4">
-        <v>45953.708333333299</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="4">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H21" s="4">
-        <v>45953.708333333299</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" t="s">
-        <v>6</v>
-      </c>
-      <c r="K21" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" t="s">
         <v>58</v>
       </c>
-      <c r="B22" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
+      <c r="C22" s="4">
+        <v>45940.333333333299</v>
       </c>
       <c r="D22" s="4">
+        <v>45946.708333333299</v>
+      </c>
+      <c r="E22" s="4">
         <v>45940.333333333299</v>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" s="4">
         <v>45946.708333333299</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="4">
-        <v>45940.333333333299</v>
-      </c>
-      <c r="H22" s="4">
-        <v>45946.708333333299</v>
+      <c r="G22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
         <v>60</v>
       </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>5</v>
+      <c r="C23" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D23" s="4">
+        <v>45932.708333333299</v>
+      </c>
+      <c r="E23" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <v>45932.708333333299</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H23" s="4">
-        <v>45932.708333333299</v>
+      <c r="G23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>5</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
         <v>62</v>
       </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
+      <c r="C24" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D24" s="4">
+        <v>45960.708333333299</v>
+      </c>
+      <c r="E24" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <v>45960.708333333299</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H24" s="4">
-        <v>45960.708333333299</v>
+      <c r="G24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" t="s">
         <v>64</v>
       </c>
-      <c r="B25" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
+      <c r="C25" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D25" s="4">
+        <v>45954.708333333299</v>
+      </c>
+      <c r="E25" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" s="4">
         <v>45954.708333333299</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H25" s="4">
-        <v>45954.708333333299</v>
+      <c r="G25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>5</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
         <v>66</v>
       </c>
-      <c r="B26" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
+      <c r="C26" s="4">
+        <v>45981.333333333299</v>
       </c>
       <c r="D26" s="4">
+        <v>45999.708333333299</v>
+      </c>
+      <c r="E26" s="4">
         <v>45981.333333333299</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <v>45999.708333333299</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="4">
-        <v>45981.333333333299</v>
-      </c>
-      <c r="H26" s="4">
-        <v>45999.708333333299</v>
+      <c r="G26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>5</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
         <v>68</v>
       </c>
-      <c r="B27" t="s">
-        <v>69</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>5</v>
+      <c r="C27" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D27" s="4">
+        <v>45975.708333333299</v>
+      </c>
+      <c r="E27" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" s="4">
         <v>45975.708333333299</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H27" s="4">
-        <v>45975.708333333299</v>
+      <c r="G27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" t="s">
+        <v>5</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K27" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
         <v>70</v>
       </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>5</v>
+      <c r="C28" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D28" s="4">
+        <v>45936.708333333299</v>
+      </c>
+      <c r="E28" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" s="4">
         <v>45936.708333333299</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H28" s="4">
-        <v>45936.708333333299</v>
+      <c r="G28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" t="s">
+        <v>5</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J28" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K28" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
         <v>72</v>
       </c>
-      <c r="B29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>5</v>
+      <c r="C29" s="4">
+        <v>45905.333333333299</v>
       </c>
       <c r="D29" s="4">
+        <v>45918.708333333299</v>
+      </c>
+      <c r="E29" s="4">
         <v>45905.333333333299</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <v>45918.708333333299</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="4">
-        <v>45905.333333333299</v>
-      </c>
-      <c r="H29" s="4">
-        <v>45918.708333333299</v>
+      <c r="G29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="C30" s="4">
+        <v>46192.333333333299</v>
       </c>
       <c r="D30" s="4">
         <v>46192.333333333299</v>
       </c>
       <c r="E30" s="4">
-        <v>46192.333333333299</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G30" s="4">
         <v>46171.333333333299</v>
       </c>
-      <c r="H30" s="4">
+      <c r="F30" s="4">
         <v>46171.333333333299</v>
       </c>
+      <c r="G30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="s">
+        <v>4</v>
+      </c>
       <c r="I30" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J30" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K30" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
         <v>76</v>
       </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>5</v>
+      <c r="C31" s="4">
+        <v>45950.333333333299</v>
       </c>
       <c r="D31" s="4">
+        <v>45953.708333333299</v>
+      </c>
+      <c r="E31" s="4">
         <v>45950.333333333299</v>
       </c>
-      <c r="E31" s="4">
+      <c r="F31" s="4">
         <v>45953.708333333299</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G31" s="4">
-        <v>45950.333333333299</v>
-      </c>
-      <c r="H31" s="4">
-        <v>45953.708333333299</v>
+      <c r="G31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" t="s">
+        <v>5</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J31" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" t="s">
         <v>78</v>
       </c>
-      <c r="B32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>5</v>
+      <c r="C32" s="4">
+        <v>45933.333333333299</v>
       </c>
       <c r="D32" s="4">
+        <v>45947.708333333299</v>
+      </c>
+      <c r="E32" s="4">
         <v>45933.333333333299</v>
       </c>
-      <c r="E32" s="4">
+      <c r="F32" s="4">
         <v>45947.708333333299</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="4">
-        <v>45933.333333333299</v>
-      </c>
-      <c r="H32" s="4">
-        <v>45947.708333333299</v>
+      <c r="G32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" t="s">
+        <v>5</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K32" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
+        <v>79</v>
+      </c>
+      <c r="B33" t="s">
         <v>80</v>
       </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>5</v>
+      <c r="C33" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D33" s="4">
+        <v>45947.708333333299</v>
+      </c>
+      <c r="E33" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E33" s="4">
+      <c r="F33" s="4">
         <v>45947.708333333299</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H33" s="4">
-        <v>45947.708333333299</v>
+      <c r="G33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" t="s">
+        <v>5</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K33" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
         <v>82</v>
       </c>
-      <c r="B34" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>5</v>
+      <c r="C34" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D34" s="4">
+        <v>45947.708333333299</v>
+      </c>
+      <c r="E34" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E34" s="4">
+      <c r="F34" s="4">
         <v>45947.708333333299</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H34" s="4">
-        <v>45947.708333333299</v>
+      <c r="G34" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>5</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J34" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" t="s">
         <v>84</v>
       </c>
-      <c r="B35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>5</v>
+      <c r="C35" s="4">
+        <v>45957.708333333299</v>
       </c>
       <c r="D35" s="4">
+        <v>46010.708333333299</v>
+      </c>
+      <c r="E35" s="4">
         <v>45957.708333333299</v>
       </c>
-      <c r="E35" s="4">
+      <c r="F35" s="4">
         <v>46010.708333333299</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="4">
-        <v>45957.708333333299</v>
-      </c>
-      <c r="H35" s="4">
-        <v>46010.708333333299</v>
+      <c r="G35" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H35" t="s">
+        <v>5</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K35" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
         <v>86</v>
       </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>5</v>
+      <c r="C36" s="4">
+        <v>45965.333333333299</v>
       </c>
       <c r="D36" s="4">
+        <v>45974.708333333299</v>
+      </c>
+      <c r="E36" s="4">
         <v>45965.333333333299</v>
       </c>
-      <c r="E36" s="4">
+      <c r="F36" s="4">
         <v>45974.708333333299</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="4">
-        <v>45965.333333333299</v>
-      </c>
-      <c r="H36" s="4">
-        <v>45974.708333333299</v>
+      <c r="G36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H36" t="s">
+        <v>5</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K36" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" t="s">
         <v>88</v>
       </c>
-      <c r="B37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>5</v>
+      <c r="C37" s="4">
+        <v>45958.333333333299</v>
       </c>
       <c r="D37" s="4">
+        <v>45960.708333333299</v>
+      </c>
+      <c r="E37" s="4">
         <v>45958.333333333299</v>
       </c>
-      <c r="E37" s="4">
+      <c r="F37" s="4">
         <v>45960.708333333299</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="4">
-        <v>45958.333333333299</v>
-      </c>
-      <c r="H37" s="4">
-        <v>45960.708333333299</v>
+      <c r="G37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H37" t="s">
+        <v>5</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J37" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K37" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
         <v>90</v>
       </c>
-      <c r="B38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>5</v>
+      <c r="C38" s="4">
+        <v>46010.333333333299</v>
       </c>
       <c r="D38" s="4">
         <v>46010.333333333299</v>
@@ -2420,384 +2402,384 @@
       <c r="E38" s="4">
         <v>46010.333333333299</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G38" s="4">
+      <c r="F38" s="4">
         <v>46010.333333333299</v>
       </c>
-      <c r="H38" s="4">
-        <v>46010.333333333299</v>
+      <c r="G38" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" t="s">
+        <v>5</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J38" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K38" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" t="s">
         <v>92</v>
       </c>
-      <c r="B39" t="s">
-        <v>93</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>5</v>
+      <c r="C39" s="4">
+        <v>46000.333333333299</v>
       </c>
       <c r="D39" s="4">
+        <v>46002.708333333299</v>
+      </c>
+      <c r="E39" s="4">
         <v>46000.333333333299</v>
       </c>
-      <c r="E39" s="4">
+      <c r="F39" s="4">
         <v>46002.708333333299</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46000.333333333299</v>
-      </c>
-      <c r="H39" s="4">
-        <v>46002.708333333299</v>
+      <c r="G39" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" t="s">
+        <v>5</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J39" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K39" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
         <v>94</v>
       </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>5</v>
+      <c r="C40" s="4">
+        <v>45992.333333333299</v>
       </c>
       <c r="D40" s="4">
+        <v>45996.708333333299</v>
+      </c>
+      <c r="E40" s="4">
         <v>45992.333333333299</v>
       </c>
-      <c r="E40" s="4">
+      <c r="F40" s="4">
         <v>45996.708333333299</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="4">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="H40" s="4">
-        <v>45996.708333333299</v>
+      <c r="G40" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H40" t="s">
+        <v>5</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J40" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K40" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" t="s">
         <v>96</v>
       </c>
-      <c r="B41" t="s">
-        <v>97</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>5</v>
+      <c r="C41" s="4">
+        <v>45974.333333333299</v>
       </c>
       <c r="D41" s="4">
+        <v>45989.708333333299</v>
+      </c>
+      <c r="E41" s="4">
         <v>45974.333333333299</v>
       </c>
-      <c r="E41" s="4">
+      <c r="F41" s="4">
         <v>45989.708333333299</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="4">
-        <v>45974.333333333299</v>
-      </c>
-      <c r="H41" s="4">
-        <v>45989.708333333299</v>
+      <c r="G41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H41" t="s">
+        <v>5</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
+        <v>97</v>
+      </c>
+      <c r="B42" t="s">
         <v>98</v>
       </c>
-      <c r="B42" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>5</v>
+      <c r="C42" s="4">
+        <v>45980.333333333299</v>
       </c>
       <c r="D42" s="4">
+        <v>45989.708333333299</v>
+      </c>
+      <c r="E42" s="4">
         <v>45980.333333333299</v>
       </c>
-      <c r="E42" s="4">
+      <c r="F42" s="4">
         <v>45989.708333333299</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="4">
-        <v>45980.333333333299</v>
-      </c>
-      <c r="H42" s="4">
-        <v>45989.708333333299</v>
+      <c r="G42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H42" t="s">
+        <v>5</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
         <v>100</v>
       </c>
-      <c r="B43" t="s">
-        <v>101</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>5</v>
+      <c r="C43" s="4">
+        <v>45972.333333333299</v>
       </c>
       <c r="D43" s="4">
+        <v>45975.333333333299</v>
+      </c>
+      <c r="E43" s="4">
         <v>45972.333333333299</v>
       </c>
-      <c r="E43" s="4">
+      <c r="F43" s="4">
         <v>45975.333333333299</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="4">
-        <v>45972.333333333299</v>
-      </c>
-      <c r="H43" s="4">
-        <v>45975.333333333299</v>
+      <c r="G43" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H43" t="s">
+        <v>5</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J43" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
+        <v>101</v>
+      </c>
+      <c r="B44" t="s">
         <v>102</v>
       </c>
-      <c r="B44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>5</v>
+      <c r="C44" s="4">
+        <v>45992.333333333299</v>
       </c>
       <c r="D44" s="4">
+        <v>46010.708333333299</v>
+      </c>
+      <c r="E44" s="4">
         <v>45992.333333333299</v>
       </c>
-      <c r="E44" s="4">
+      <c r="F44" s="4">
         <v>46010.708333333299</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G44" s="4">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="H44" s="4">
-        <v>46010.708333333299</v>
+      <c r="G44" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H44" t="s">
+        <v>5</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J44" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" t="s">
         <v>104</v>
       </c>
-      <c r="B45" t="s">
-        <v>105</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>5</v>
+      <c r="C45" s="4">
+        <v>45964.333333333299</v>
       </c>
       <c r="D45" s="4">
+        <v>45966.708333333299</v>
+      </c>
+      <c r="E45" s="4">
         <v>45964.333333333299</v>
       </c>
-      <c r="E45" s="4">
+      <c r="F45" s="4">
         <v>45966.708333333299</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="4">
-        <v>45964.333333333299</v>
-      </c>
-      <c r="H45" s="4">
-        <v>45966.708333333299</v>
+      <c r="G45" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H45" t="s">
+        <v>5</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B46" t="s">
         <v>106</v>
       </c>
-      <c r="B46" t="s">
-        <v>107</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>5</v>
+      <c r="C46" s="4">
+        <v>45978.333333333299</v>
       </c>
       <c r="D46" s="4">
+        <v>45988.708333333299</v>
+      </c>
+      <c r="E46" s="4">
         <v>45978.333333333299</v>
       </c>
-      <c r="E46" s="4">
+      <c r="F46" s="4">
         <v>45988.708333333299</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" s="4">
-        <v>45978.333333333299</v>
-      </c>
-      <c r="H46" s="4">
-        <v>45988.708333333299</v>
+      <c r="G46" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H46" t="s">
+        <v>5</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J46" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
         <v>108</v>
       </c>
-      <c r="B47" t="s">
-        <v>109</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>5</v>
+      <c r="C47" s="4">
+        <v>45937.333333333299</v>
       </c>
       <c r="D47" s="4">
+        <v>45943.708333333299</v>
+      </c>
+      <c r="E47" s="4">
         <v>45937.333333333299</v>
       </c>
-      <c r="E47" s="4">
+      <c r="F47" s="4">
         <v>45943.708333333299</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="4">
-        <v>45937.333333333299</v>
-      </c>
-      <c r="H47" s="4">
-        <v>45943.708333333299</v>
+      <c r="G47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H47" t="s">
+        <v>5</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
+        <v>109</v>
+      </c>
+      <c r="B48" t="s">
         <v>110</v>
       </c>
-      <c r="B48" t="s">
-        <v>111</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>5</v>
+      <c r="C48" s="4">
+        <v>45957.333333333299</v>
       </c>
       <c r="D48" s="4">
+        <v>45957.708333333299</v>
+      </c>
+      <c r="E48" s="4">
         <v>45957.333333333299</v>
       </c>
-      <c r="E48" s="4">
+      <c r="F48" s="4">
         <v>45957.708333333299</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="4">
-        <v>45957.333333333299</v>
-      </c>
-      <c r="H48" s="4">
-        <v>45957.708333333299</v>
+      <c r="G48" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H48" t="s">
+        <v>5</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J48" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" t="s">
         <v>112</v>
       </c>
-      <c r="B49" t="s">
-        <v>113</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>5</v>
+      <c r="C49" s="4">
+        <v>45947.333333333299</v>
       </c>
       <c r="D49" s="4">
         <v>45947.333333333299</v>
@@ -2805,629 +2787,629 @@
       <c r="E49" s="4">
         <v>45947.333333333299</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="F49" s="4">
         <v>45947.333333333299</v>
       </c>
-      <c r="H49" s="4">
-        <v>45947.333333333299</v>
+      <c r="G49" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H49" t="s">
+        <v>5</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J49" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
+        <v>113</v>
+      </c>
+      <c r="B50" t="s">
         <v>114</v>
       </c>
-      <c r="B50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>5</v>
+      <c r="C50" s="4">
+        <v>45919.333333333299</v>
       </c>
       <c r="D50" s="4">
+        <v>45946.708333333299</v>
+      </c>
+      <c r="E50" s="4">
         <v>45919.333333333299</v>
       </c>
-      <c r="E50" s="4">
+      <c r="F50" s="4">
         <v>45946.708333333299</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="4">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H50" s="4">
-        <v>45946.708333333299</v>
+      <c r="G50" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H50" t="s">
+        <v>5</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J50" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
         <v>116</v>
       </c>
-      <c r="B51" t="s">
-        <v>117</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>5</v>
+      <c r="C51" s="4">
+        <v>46083.333333333299</v>
       </c>
       <c r="D51" s="4">
+        <v>46090.708333333299</v>
+      </c>
+      <c r="E51" s="4">
         <v>46083.333333333299</v>
       </c>
-      <c r="E51" s="4">
+      <c r="F51" s="4">
         <v>46090.708333333299</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="4">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="H51" s="4">
-        <v>46090.708333333299</v>
+      <c r="G51" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H51" t="s">
+        <v>5</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J51" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" t="s">
         <v>118</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" s="4">
+        <v>46184.333333333299</v>
+      </c>
+      <c r="D52" s="4">
+        <v>46191.708333333299</v>
+      </c>
+      <c r="E52" s="4">
+        <v>46162.333333333299</v>
+      </c>
+      <c r="F52" s="4">
+        <v>46170.708333333299</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H52" t="s">
+        <v>4</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D52" s="4">
-        <v>46184.333333333299</v>
-      </c>
-      <c r="E52" s="4">
-        <v>46191.708333333299</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="4">
-        <v>46162.333333333299</v>
-      </c>
-      <c r="H52" s="4">
-        <v>46170.708333333299</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J52" t="s">
-        <v>5</v>
+      <c r="J52" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K52" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
+        <v>120</v>
+      </c>
+      <c r="B53" t="s">
         <v>121</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" s="4">
+        <v>46181.333333333299</v>
+      </c>
+      <c r="D53" s="4">
+        <v>46183.708333333299</v>
+      </c>
+      <c r="E53" s="4">
+        <v>46157.333333333299</v>
+      </c>
+      <c r="F53" s="4">
+        <v>46161.708333333299</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H53" t="s">
+        <v>4</v>
+      </c>
+      <c r="I53" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D53" s="4">
-        <v>46181.333333333299</v>
-      </c>
-      <c r="E53" s="4">
-        <v>46183.708333333299</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G53" s="4">
-        <v>46157.333333333299</v>
-      </c>
-      <c r="H53" s="4">
-        <v>46161.708333333299</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J53" t="s">
-        <v>5</v>
+      <c r="J53" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" t="s">
         <v>124</v>
       </c>
-      <c r="B54" t="s">
-        <v>125</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>30</v>
+      <c r="C54" s="4">
+        <v>46177.333333333299</v>
       </c>
       <c r="D54" s="4">
-        <v>46177.333333333299</v>
+        <v>46178.708333333299</v>
       </c>
       <c r="E54" s="4">
-        <v>46178.708333333299</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G54" s="4">
         <v>46155.333333333299</v>
       </c>
-      <c r="H54" s="4">
+      <c r="F54" s="4">
         <v>46156.708333333299</v>
       </c>
+      <c r="G54" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H54" t="s">
+        <v>4</v>
+      </c>
       <c r="I54" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J54" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
+        <v>125</v>
+      </c>
+      <c r="B55" t="s">
         <v>126</v>
       </c>
-      <c r="B55" t="s">
-        <v>127</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>30</v>
+      <c r="C55" s="4">
+        <v>46175.333333333299</v>
       </c>
       <c r="D55" s="4">
-        <v>46175.333333333299</v>
+        <v>46176.708333333299</v>
       </c>
       <c r="E55" s="4">
-        <v>46176.708333333299</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G55" s="4">
         <v>46153.333333333299</v>
       </c>
-      <c r="H55" s="4">
+      <c r="F55" s="4">
         <v>46154.708333333299</v>
       </c>
+      <c r="G55" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H55" t="s">
+        <v>4</v>
+      </c>
       <c r="I55" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J55" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" t="s">
         <v>128</v>
       </c>
-      <c r="B56" t="s">
-        <v>129</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>30</v>
+      <c r="C56" s="4">
+        <v>46171.333333333299</v>
       </c>
       <c r="D56" s="4">
-        <v>46171.333333333299</v>
+        <v>46174.708333333299</v>
       </c>
       <c r="E56" s="4">
-        <v>46174.708333333299</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G56" s="4">
         <v>46149.333333333299</v>
       </c>
-      <c r="H56" s="4">
+      <c r="F56" s="4">
         <v>46150.708333333299</v>
       </c>
+      <c r="G56" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H56" t="s">
+        <v>4</v>
+      </c>
       <c r="I56" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J56" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" t="s">
         <v>130</v>
       </c>
-      <c r="B57" t="s">
-        <v>131</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>30</v>
+      <c r="C57" s="4">
+        <v>46169.333333333299</v>
       </c>
       <c r="D57" s="4">
-        <v>46169.333333333299</v>
+        <v>46170.708333333299</v>
       </c>
       <c r="E57" s="4">
-        <v>46170.708333333299</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G57" s="4">
         <v>46147.333333333299</v>
       </c>
-      <c r="H57" s="4">
+      <c r="F57" s="4">
         <v>46148.708333333299</v>
       </c>
+      <c r="G57" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" t="s">
+        <v>4</v>
+      </c>
       <c r="I57" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J57" t="s">
-        <v>5</v>
+        <v>29</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" t="s">
         <v>132</v>
       </c>
-      <c r="B58" t="s">
-        <v>133</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>43</v>
+      <c r="C58" s="4">
+        <v>46168.333333333299</v>
       </c>
       <c r="D58" s="4">
-        <v>46168.333333333299</v>
+        <v>46168.708333333299</v>
       </c>
       <c r="E58" s="4">
-        <v>46168.708333333299</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G58" s="4">
         <v>46143.333333333299</v>
       </c>
-      <c r="H58" s="4">
+      <c r="F58" s="4">
         <v>46143.708333333299</v>
       </c>
+      <c r="G58" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H58" t="s">
+        <v>4</v>
+      </c>
       <c r="I58" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J58" t="s">
-        <v>5</v>
+        <v>42</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K58" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" t="s">
         <v>134</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" s="4">
+        <v>46112.333333333299</v>
+      </c>
+      <c r="D59" s="4">
+        <v>46167.708333333299</v>
+      </c>
+      <c r="E59" s="4">
+        <v>46112.333333333299</v>
+      </c>
+      <c r="F59" s="4">
+        <v>46142.708333333299</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H59" t="s">
+        <v>4</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D59" s="4">
-        <v>46112.333333333299</v>
-      </c>
-      <c r="E59" s="4">
-        <v>46167.708333333299</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G59" s="4">
-        <v>46112.333333333299</v>
-      </c>
-      <c r="H59" s="4">
-        <v>46142.708333333299</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J59" t="s">
-        <v>5</v>
+      <c r="J59" s="2" t="s">
+        <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60" t="s">
         <v>138</v>
       </c>
-      <c r="B60" t="s">
-        <v>139</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>5</v>
+      <c r="C60" s="4">
+        <v>46111.333333333299</v>
       </c>
       <c r="D60" s="4">
+        <v>46111.708333333299</v>
+      </c>
+      <c r="E60" s="4">
         <v>46111.333333333299</v>
       </c>
-      <c r="E60" s="4">
+      <c r="F60" s="4">
         <v>46111.708333333299</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46111.333333333299</v>
-      </c>
-      <c r="H60" s="4">
-        <v>46111.708333333299</v>
+      <c r="G60" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H60" t="s">
+        <v>5</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J60" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" t="s">
         <v>140</v>
       </c>
-      <c r="B61" t="s">
-        <v>141</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>5</v>
+      <c r="C61" s="4">
+        <v>46080.333333333299</v>
       </c>
       <c r="D61" s="4">
+        <v>46080.708333333299</v>
+      </c>
+      <c r="E61" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="E61" s="4">
+      <c r="F61" s="4">
         <v>46080.708333333299</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G61" s="4">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H61" s="4">
-        <v>46080.708333333299</v>
+      <c r="G61" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H61" t="s">
+        <v>5</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J61" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K61" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" t="s">
         <v>142</v>
       </c>
-      <c r="B62" t="s">
-        <v>143</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>5</v>
+      <c r="C62" s="4">
+        <v>46080.333333333299</v>
       </c>
       <c r="D62" s="4">
+        <v>46080.708333333299</v>
+      </c>
+      <c r="E62" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="E62" s="4">
+      <c r="F62" s="4">
         <v>46080.708333333299</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G62" s="4">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H62" s="4">
-        <v>46080.708333333299</v>
+      <c r="G62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H62" t="s">
+        <v>5</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J62" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K62" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
+        <v>143</v>
+      </c>
+      <c r="B63" t="s">
         <v>144</v>
       </c>
-      <c r="B63" t="s">
-        <v>145</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>5</v>
+      <c r="C63" s="4">
+        <v>46080.333333333299</v>
       </c>
       <c r="D63" s="4">
+        <v>46080.708333333299</v>
+      </c>
+      <c r="E63" s="4">
         <v>46080.333333333299</v>
       </c>
-      <c r="E63" s="4">
+      <c r="F63" s="4">
         <v>46080.708333333299</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G63" s="4">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H63" s="4">
-        <v>46080.708333333299</v>
+      <c r="G63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H63" t="s">
+        <v>5</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J63" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K63" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
+        <v>145</v>
+      </c>
+      <c r="B64" t="s">
         <v>146</v>
       </c>
-      <c r="B64" t="s">
-        <v>147</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>5</v>
+      <c r="C64" s="4">
+        <v>46076.333333333299</v>
       </c>
       <c r="D64" s="4">
+        <v>46080.708333333299</v>
+      </c>
+      <c r="E64" s="4">
         <v>46076.333333333299</v>
       </c>
-      <c r="E64" s="4">
+      <c r="F64" s="4">
         <v>46080.708333333299</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G64" s="4">
-        <v>46076.333333333299</v>
-      </c>
-      <c r="H64" s="4">
-        <v>46080.708333333299</v>
+      <c r="G64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H64" t="s">
+        <v>5</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J64" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K64" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
+        <v>147</v>
+      </c>
+      <c r="B65" t="s">
         <v>148</v>
       </c>
-      <c r="B65" t="s">
-        <v>149</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>5</v>
+      <c r="C65" s="4">
+        <v>46073.333333333299</v>
       </c>
       <c r="D65" s="4">
+        <v>46073.708333333299</v>
+      </c>
+      <c r="E65" s="4">
         <v>46073.333333333299</v>
       </c>
-      <c r="E65" s="4">
+      <c r="F65" s="4">
         <v>46073.708333333299</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G65" s="4">
-        <v>46073.333333333299</v>
-      </c>
-      <c r="H65" s="4">
-        <v>46073.708333333299</v>
+      <c r="G65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H65" t="s">
+        <v>5</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J65" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K65" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" t="s">
         <v>150</v>
       </c>
-      <c r="B66" t="s">
-        <v>151</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>5</v>
+      <c r="C66" s="4">
+        <v>46071.333333333299</v>
       </c>
       <c r="D66" s="4">
+        <v>46073.708333333299</v>
+      </c>
+      <c r="E66" s="4">
         <v>46071.333333333299</v>
       </c>
-      <c r="E66" s="4">
+      <c r="F66" s="4">
         <v>46073.708333333299</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G66" s="4">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="H66" s="4">
-        <v>46073.708333333299</v>
+      <c r="G66" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H66" t="s">
+        <v>5</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J66" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K66" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" t="s">
         <v>152</v>
       </c>
-      <c r="B67" t="s">
-        <v>153</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>5</v>
+      <c r="C67" s="4">
+        <v>46071.333333333299</v>
       </c>
       <c r="D67" s="4">
         <v>46071.333333333299</v>
@@ -3435,209 +3417,209 @@
       <c r="E67" s="4">
         <v>46071.333333333299</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="4">
+      <c r="F67" s="4">
         <v>46071.333333333299</v>
       </c>
-      <c r="H67" s="4">
-        <v>46071.333333333299</v>
+      <c r="G67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H67" t="s">
+        <v>5</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J67" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K67" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
+        <v>153</v>
+      </c>
+      <c r="B68" t="s">
         <v>154</v>
       </c>
-      <c r="B68" t="s">
-        <v>155</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>5</v>
+      <c r="C68" s="4">
+        <v>46069.333333333299</v>
       </c>
       <c r="D68" s="4">
+        <v>46070.708333333299</v>
+      </c>
+      <c r="E68" s="4">
         <v>46069.333333333299</v>
       </c>
-      <c r="E68" s="4">
+      <c r="F68" s="4">
         <v>46070.708333333299</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="4">
-        <v>46069.333333333299</v>
-      </c>
-      <c r="H68" s="4">
-        <v>46070.708333333299</v>
+      <c r="G68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H68" t="s">
+        <v>5</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J68" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K68" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
+        <v>155</v>
+      </c>
+      <c r="B69" t="s">
         <v>156</v>
       </c>
-      <c r="B69" t="s">
-        <v>157</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>5</v>
+      <c r="C69" s="4">
+        <v>46066.333333333299</v>
       </c>
       <c r="D69" s="4">
+        <v>46071.708333333299</v>
+      </c>
+      <c r="E69" s="4">
         <v>46066.333333333299</v>
       </c>
-      <c r="E69" s="4">
+      <c r="F69" s="4">
         <v>46071.708333333299</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="4">
-        <v>46066.333333333299</v>
-      </c>
-      <c r="H69" s="4">
-        <v>46071.708333333299</v>
+      <c r="G69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H69" t="s">
+        <v>5</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J69" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K69" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
+        <v>157</v>
+      </c>
+      <c r="B70" t="s">
         <v>158</v>
       </c>
-      <c r="B70" t="s">
-        <v>159</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>5</v>
+      <c r="C70" s="4">
+        <v>46062.333333333299</v>
       </c>
       <c r="D70" s="4">
+        <v>46065.708333333299</v>
+      </c>
+      <c r="E70" s="4">
         <v>46062.333333333299</v>
       </c>
-      <c r="E70" s="4">
+      <c r="F70" s="4">
         <v>46065.708333333299</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="4">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="H70" s="4">
-        <v>46065.708333333299</v>
+      <c r="G70" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H70" t="s">
+        <v>5</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J70" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K70" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
+        <v>159</v>
+      </c>
+      <c r="B71" t="s">
         <v>160</v>
       </c>
-      <c r="B71" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>5</v>
+      <c r="C71" s="4">
+        <v>46057.333333333299</v>
       </c>
       <c r="D71" s="4">
+        <v>46062.708333333299</v>
+      </c>
+      <c r="E71" s="4">
         <v>46057.333333333299</v>
       </c>
-      <c r="E71" s="4">
+      <c r="F71" s="4">
         <v>46062.708333333299</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="4">
-        <v>46057.333333333299</v>
-      </c>
-      <c r="H71" s="4">
-        <v>46062.708333333299</v>
+      <c r="G71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H71" t="s">
+        <v>5</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J71" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K71" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
+        <v>161</v>
+      </c>
+      <c r="B72" t="s">
         <v>162</v>
       </c>
-      <c r="B72" t="s">
-        <v>163</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>5</v>
+      <c r="C72" s="4">
+        <v>46055.333333333299</v>
       </c>
       <c r="D72" s="4">
+        <v>46055.708333333299</v>
+      </c>
+      <c r="E72" s="4">
         <v>46055.333333333299</v>
       </c>
-      <c r="E72" s="4">
+      <c r="F72" s="4">
         <v>46055.708333333299</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G72" s="4">
-        <v>46055.333333333299</v>
-      </c>
-      <c r="H72" s="4">
-        <v>46055.708333333299</v>
+      <c r="G72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H72" t="s">
+        <v>5</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J72" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K72" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
+        <v>163</v>
+      </c>
+      <c r="B73" t="s">
         <v>164</v>
       </c>
-      <c r="B73" t="s">
-        <v>165</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>5</v>
+      <c r="C73" s="4">
+        <v>46052.333333333299</v>
       </c>
       <c r="D73" s="4">
         <v>46052.333333333299</v>
@@ -3645,828 +3627,828 @@
       <c r="E73" s="4">
         <v>46052.333333333299</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G73" s="4">
+      <c r="F73" s="4">
         <v>46052.333333333299</v>
       </c>
-      <c r="H73" s="4">
-        <v>46052.333333333299</v>
+      <c r="G73" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H73" t="s">
+        <v>5</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J73" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
+        <v>165</v>
+      </c>
+      <c r="B74" t="s">
         <v>166</v>
       </c>
-      <c r="B74" t="s">
-        <v>167</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>5</v>
+      <c r="C74" s="4">
+        <v>46051.333333333299</v>
       </c>
       <c r="D74" s="4">
+        <v>46051.708333333299</v>
+      </c>
+      <c r="E74" s="4">
         <v>46051.333333333299</v>
       </c>
-      <c r="E74" s="4">
+      <c r="F74" s="4">
         <v>46051.708333333299</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="4">
-        <v>46051.333333333299</v>
-      </c>
-      <c r="H74" s="4">
-        <v>46051.708333333299</v>
+      <c r="G74" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H74" t="s">
+        <v>5</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J74" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
+        <v>167</v>
+      </c>
+      <c r="B75" t="s">
         <v>168</v>
       </c>
-      <c r="B75" t="s">
-        <v>169</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>5</v>
+      <c r="C75" s="4">
+        <v>46050.333333333299</v>
       </c>
       <c r="D75" s="4">
+        <v>46050.708333333299</v>
+      </c>
+      <c r="E75" s="4">
         <v>46050.333333333299</v>
       </c>
-      <c r="E75" s="4">
+      <c r="F75" s="4">
         <v>46050.708333333299</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" s="4">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="H75" s="4">
-        <v>46050.708333333299</v>
+      <c r="G75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H75" t="s">
+        <v>5</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J75" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K75" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
+        <v>169</v>
+      </c>
+      <c r="B76" t="s">
         <v>170</v>
       </c>
-      <c r="B76" t="s">
-        <v>171</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>5</v>
+      <c r="C76" s="4">
+        <v>46050.333333333299</v>
       </c>
       <c r="D76" s="4">
+        <v>46052.708333333299</v>
+      </c>
+      <c r="E76" s="4">
         <v>46050.333333333299</v>
       </c>
-      <c r="E76" s="4">
+      <c r="F76" s="4">
         <v>46052.708333333299</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="4">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="H76" s="4">
-        <v>46052.708333333299</v>
+      <c r="G76" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H76" t="s">
+        <v>5</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J76" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K76" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" t="s">
         <v>172</v>
       </c>
-      <c r="B77" t="s">
-        <v>173</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>5</v>
+      <c r="C77" s="4">
+        <v>46048.333333333299</v>
       </c>
       <c r="D77" s="4">
+        <v>46049.708333333299</v>
+      </c>
+      <c r="E77" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="E77" s="4">
+      <c r="F77" s="4">
         <v>46049.708333333299</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G77" s="4">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H77" s="4">
-        <v>46049.708333333299</v>
+      <c r="G77" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H77" t="s">
+        <v>5</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J77" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K77" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
+        <v>173</v>
+      </c>
+      <c r="B78" t="s">
         <v>174</v>
       </c>
-      <c r="B78" t="s">
-        <v>175</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>5</v>
+      <c r="C78" s="4">
+        <v>46048.333333333299</v>
       </c>
       <c r="D78" s="4">
+        <v>46052.708333333299</v>
+      </c>
+      <c r="E78" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="E78" s="4">
+      <c r="F78" s="4">
         <v>46052.708333333299</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78" s="4">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H78" s="4">
-        <v>46052.708333333299</v>
+      <c r="G78" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H78" t="s">
+        <v>5</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J78" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K78" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
+        <v>175</v>
+      </c>
+      <c r="B79" t="s">
         <v>176</v>
       </c>
-      <c r="B79" t="s">
-        <v>177</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>5</v>
+      <c r="C79" s="4">
+        <v>46048.333333333299</v>
       </c>
       <c r="D79" s="4">
+        <v>46048.708333333299</v>
+      </c>
+      <c r="E79" s="4">
         <v>46048.333333333299</v>
       </c>
-      <c r="E79" s="4">
+      <c r="F79" s="4">
         <v>46048.708333333299</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G79" s="4">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H79" s="4">
-        <v>46048.708333333299</v>
+      <c r="G79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H79" t="s">
+        <v>5</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J79" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
+        <v>177</v>
+      </c>
+      <c r="B80" t="s">
         <v>178</v>
       </c>
-      <c r="B80" t="s">
-        <v>179</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>5</v>
+      <c r="C80" s="4">
+        <v>46045.333333333299</v>
       </c>
       <c r="D80" s="4">
+        <v>46045.708333333299</v>
+      </c>
+      <c r="E80" s="4">
         <v>46045.333333333299</v>
       </c>
-      <c r="E80" s="4">
+      <c r="F80" s="4">
         <v>46045.708333333299</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G80" s="4">
-        <v>46045.333333333299</v>
-      </c>
-      <c r="H80" s="4">
-        <v>46045.708333333299</v>
+      <c r="G80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H80" t="s">
+        <v>5</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J80" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K80" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
+        <v>179</v>
+      </c>
+      <c r="B81" t="s">
         <v>180</v>
       </c>
-      <c r="B81" t="s">
-        <v>181</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>5</v>
+      <c r="C81" s="4">
+        <v>46044.333333333299</v>
       </c>
       <c r="D81" s="4">
+        <v>46044.708333333299</v>
+      </c>
+      <c r="E81" s="4">
         <v>46044.333333333299</v>
       </c>
-      <c r="E81" s="4">
+      <c r="F81" s="4">
         <v>46044.708333333299</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="4">
-        <v>46044.333333333299</v>
-      </c>
-      <c r="H81" s="4">
-        <v>46044.708333333299</v>
+      <c r="G81" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H81" t="s">
+        <v>5</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K81" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" t="s">
         <v>182</v>
       </c>
-      <c r="B82" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>5</v>
+      <c r="C82" s="4">
+        <v>46043.333333333299</v>
       </c>
       <c r="D82" s="4">
+        <v>46043.708333333299</v>
+      </c>
+      <c r="E82" s="4">
         <v>46043.333333333299</v>
       </c>
-      <c r="E82" s="4">
+      <c r="F82" s="4">
         <v>46043.708333333299</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G82" s="4">
-        <v>46043.333333333299</v>
-      </c>
-      <c r="H82" s="4">
-        <v>46043.708333333299</v>
+      <c r="G82" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H82" t="s">
+        <v>5</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J82" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K82" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
+        <v>183</v>
+      </c>
+      <c r="B83" t="s">
         <v>184</v>
       </c>
-      <c r="B83" t="s">
-        <v>185</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>5</v>
+      <c r="C83" s="4">
+        <v>46042.333333333299</v>
       </c>
       <c r="D83" s="4">
+        <v>46043.708333333299</v>
+      </c>
+      <c r="E83" s="4">
         <v>46042.333333333299</v>
       </c>
-      <c r="E83" s="4">
+      <c r="F83" s="4">
         <v>46043.708333333299</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G83" s="4">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="H83" s="4">
-        <v>46043.708333333299</v>
+      <c r="G83" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H83" t="s">
+        <v>5</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K83" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
+        <v>185</v>
+      </c>
+      <c r="B84" t="s">
         <v>186</v>
       </c>
-      <c r="B84" t="s">
-        <v>187</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>5</v>
+      <c r="C84" s="4">
+        <v>46042.333333333299</v>
       </c>
       <c r="D84" s="4">
+        <v>46043.708333333299</v>
+      </c>
+      <c r="E84" s="4">
         <v>46042.333333333299</v>
       </c>
-      <c r="E84" s="4">
+      <c r="F84" s="4">
         <v>46043.708333333299</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G84" s="4">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="H84" s="4">
-        <v>46043.708333333299</v>
+      <c r="G84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H84" t="s">
+        <v>5</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J84" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
+        <v>187</v>
+      </c>
+      <c r="B85" t="s">
         <v>188</v>
       </c>
-      <c r="B85" t="s">
-        <v>189</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>5</v>
+      <c r="C85" s="4">
+        <v>46041.333333333299</v>
       </c>
       <c r="D85" s="4">
+        <v>46041.708333333299</v>
+      </c>
+      <c r="E85" s="4">
         <v>46041.333333333299</v>
       </c>
-      <c r="E85" s="4">
+      <c r="F85" s="4">
         <v>46041.708333333299</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G85" s="4">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="H85" s="4">
-        <v>46041.708333333299</v>
+      <c r="G85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H85" t="s">
+        <v>5</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J85" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" t="s">
         <v>190</v>
       </c>
-      <c r="B86" t="s">
-        <v>191</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>5</v>
+      <c r="C86" s="4">
+        <v>46041.333333333299</v>
       </c>
       <c r="D86" s="4">
+        <v>46041.708333333299</v>
+      </c>
+      <c r="E86" s="4">
         <v>46041.333333333299</v>
       </c>
-      <c r="E86" s="4">
+      <c r="F86" s="4">
         <v>46041.708333333299</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G86" s="4">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="H86" s="4">
-        <v>46041.708333333299</v>
+      <c r="G86" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H86" t="s">
+        <v>5</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J86" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K86" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
+        <v>191</v>
+      </c>
+      <c r="B87" t="s">
         <v>192</v>
       </c>
-      <c r="B87" t="s">
-        <v>193</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>5</v>
+      <c r="C87" s="4">
+        <v>46038.333333333299</v>
       </c>
       <c r="D87" s="4">
+        <v>46038.708333333299</v>
+      </c>
+      <c r="E87" s="4">
         <v>46038.333333333299</v>
       </c>
-      <c r="E87" s="4">
+      <c r="F87" s="4">
         <v>46038.708333333299</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="4">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="H87" s="4">
-        <v>46038.708333333299</v>
+      <c r="G87" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H87" t="s">
+        <v>5</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J87" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K87" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
+        <v>193</v>
+      </c>
+      <c r="B88" t="s">
         <v>194</v>
       </c>
-      <c r="B88" t="s">
-        <v>195</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>5</v>
+      <c r="C88" s="4">
+        <v>46038.333333333299</v>
       </c>
       <c r="D88" s="4">
+        <v>46038.708333333299</v>
+      </c>
+      <c r="E88" s="4">
         <v>46038.333333333299</v>
       </c>
-      <c r="E88" s="4">
+      <c r="F88" s="4">
         <v>46038.708333333299</v>
       </c>
-      <c r="F88" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G88" s="4">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="H88" s="4">
-        <v>46038.708333333299</v>
+      <c r="G88" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H88" t="s">
+        <v>5</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J88" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K88" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
+        <v>195</v>
+      </c>
+      <c r="B89" t="s">
         <v>196</v>
       </c>
-      <c r="B89" t="s">
-        <v>197</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>5</v>
+      <c r="C89" s="4">
+        <v>46036.333333333299</v>
       </c>
       <c r="D89" s="4">
+        <v>46036.708333333299</v>
+      </c>
+      <c r="E89" s="4">
         <v>46036.333333333299</v>
       </c>
-      <c r="E89" s="4">
+      <c r="F89" s="4">
         <v>46036.708333333299</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" s="4">
-        <v>46036.333333333299</v>
-      </c>
-      <c r="H89" s="4">
-        <v>46036.708333333299</v>
+      <c r="G89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H89" t="s">
+        <v>5</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K89" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
+        <v>197</v>
+      </c>
+      <c r="B90" t="s">
         <v>198</v>
       </c>
-      <c r="B90" t="s">
-        <v>199</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>5</v>
+      <c r="C90" s="4">
+        <v>46035.333333333299</v>
       </c>
       <c r="D90" s="4">
+        <v>46036.708333333299</v>
+      </c>
+      <c r="E90" s="4">
         <v>46035.333333333299</v>
       </c>
-      <c r="E90" s="4">
+      <c r="F90" s="4">
         <v>46036.708333333299</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G90" s="4">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="H90" s="4">
-        <v>46036.708333333299</v>
+      <c r="G90" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H90" t="s">
+        <v>5</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J90" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K90" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
+        <v>199</v>
+      </c>
+      <c r="B91" t="s">
         <v>200</v>
       </c>
-      <c r="B91" t="s">
-        <v>201</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>5</v>
+      <c r="C91" s="4">
+        <v>46035.333333333299</v>
       </c>
       <c r="D91" s="4">
+        <v>46035.708333333299</v>
+      </c>
+      <c r="E91" s="4">
         <v>46035.333333333299</v>
       </c>
-      <c r="E91" s="4">
+      <c r="F91" s="4">
         <v>46035.708333333299</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G91" s="4">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="H91" s="4">
-        <v>46035.708333333299</v>
+      <c r="G91" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H91" t="s">
+        <v>5</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J91" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K91" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" t="s">
         <v>202</v>
       </c>
-      <c r="B92" t="s">
-        <v>203</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>5</v>
+      <c r="C92" s="4">
+        <v>46034.333333333299</v>
       </c>
       <c r="D92" s="4">
+        <v>46034.708333333299</v>
+      </c>
+      <c r="E92" s="4">
         <v>46034.333333333299</v>
       </c>
-      <c r="E92" s="4">
+      <c r="F92" s="4">
         <v>46034.708333333299</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G92" s="4">
-        <v>46034.333333333299</v>
-      </c>
-      <c r="H92" s="4">
-        <v>46034.708333333299</v>
+      <c r="G92" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H92" t="s">
+        <v>5</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J92" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K92" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" t="s">
         <v>204</v>
       </c>
-      <c r="B93" t="s">
-        <v>205</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>5</v>
+      <c r="C93" s="4">
+        <v>46031.333333333299</v>
       </c>
       <c r="D93" s="4">
+        <v>46031.708333333299</v>
+      </c>
+      <c r="E93" s="4">
         <v>46031.333333333299</v>
       </c>
-      <c r="E93" s="4">
+      <c r="F93" s="4">
         <v>46031.708333333299</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G93" s="4">
-        <v>46031.333333333299</v>
-      </c>
-      <c r="H93" s="4">
-        <v>46031.708333333299</v>
+      <c r="G93" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H93" t="s">
+        <v>5</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J93" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K93" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B94" t="s">
-        <v>69</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>5</v>
+        <v>68</v>
+      </c>
+      <c r="C94" s="4">
+        <v>46029.333333333299</v>
       </c>
       <c r="D94" s="4">
+        <v>46041.708333333299</v>
+      </c>
+      <c r="E94" s="4">
         <v>46029.333333333299</v>
       </c>
-      <c r="E94" s="4">
+      <c r="F94" s="4">
         <v>46041.708333333299</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G94" s="4">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H94" s="4">
-        <v>46041.708333333299</v>
+      <c r="G94" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H94" t="s">
+        <v>5</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K94" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" t="s">
         <v>207</v>
       </c>
-      <c r="B95" t="s">
-        <v>208</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>5</v>
+      <c r="C95" s="4">
+        <v>46029.333333333299</v>
       </c>
       <c r="D95" s="4">
+        <v>46030.708333333299</v>
+      </c>
+      <c r="E95" s="4">
         <v>46029.333333333299</v>
       </c>
-      <c r="E95" s="4">
+      <c r="F95" s="4">
         <v>46030.708333333299</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G95" s="4">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H95" s="4">
-        <v>46030.708333333299</v>
+      <c r="G95" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H95" t="s">
+        <v>5</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J95" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K95" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
+        <v>208</v>
+      </c>
+      <c r="B96" t="s">
         <v>209</v>
       </c>
-      <c r="B96" t="s">
-        <v>210</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>5</v>
+      <c r="C96" s="4">
+        <v>45947.333333333299</v>
       </c>
       <c r="D96" s="4">
+        <v>45980.708333333299</v>
+      </c>
+      <c r="E96" s="4">
         <v>45947.333333333299</v>
       </c>
-      <c r="E96" s="4">
+      <c r="F96" s="4">
         <v>45980.708333333299</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G96" s="4">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H96" s="4">
-        <v>45980.708333333299</v>
+      <c r="G96" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H96" t="s">
+        <v>5</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J96" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="K96" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072A8053-0446-45B9-ADEF-8A8454A4FC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC71556-E4AF-4BA1-9CDF-0181F0EAA331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="219">
   <si>
     <t>Activity ID</t>
   </si>
@@ -675,12 +675,6 @@
     <t>Activity % Complete</t>
   </si>
   <si>
-    <t>BL Start</t>
-  </si>
-  <si>
-    <t>BL Finish</t>
-  </si>
-  <si>
     <t>Remaining Duration</t>
   </si>
   <si>
@@ -691,6 +685,12 @@
   </si>
   <si>
     <t>Comments</t>
+  </si>
+  <si>
+    <t>BL1 Start</t>
+  </si>
+  <si>
+    <t>BL1 Finish</t>
   </si>
 </sst>
 </file>
@@ -700,15 +700,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -731,7 +726,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -743,7 +738,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1078,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1091,42 +1085,45 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J1" t="s">
         <v>213</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
+        <v>212</v>
+      </c>
+      <c r="L1" t="s">
         <v>216</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="K1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1161,7 +1158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1196,7 +1193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1231,7 +1228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1266,7 +1263,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1301,7 +1298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1336,7 +1333,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1406,7 +1403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1441,7 +1438,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1476,7 +1473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1511,7 +1508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1546,7 +1543,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1581,7 +1578,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1616,7 +1613,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>43</v>
       </c>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC71556-E4AF-4BA1-9CDF-0181F0EAA331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E16F8AD-8827-47EC-A19D-266CFB60DE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="219">
   <si>
     <t>Activity ID</t>
   </si>
@@ -687,10 +687,10 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>BL1 Start</t>
-  </si>
-  <si>
-    <t>BL1 Finish</t>
+    <t>BL1 Project Start</t>
+  </si>
+  <si>
+    <t>BL1 Project Finish</t>
   </si>
 </sst>
 </file>
@@ -1072,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -1085,45 +1085,42 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="2" t="s">
+        <v>210</v>
+      </c>
       <c r="D1" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G1" s="2" t="s">
         <v>218</v>
       </c>
+      <c r="G1" t="s">
+        <v>215</v>
+      </c>
       <c r="H1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1158,7 +1155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1193,7 +1190,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1228,7 +1225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1263,7 +1260,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1298,7 +1295,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1333,7 +1330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1368,7 +1365,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>23</v>
       </c>
@@ -1403,7 +1400,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -1438,7 +1435,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1473,7 +1470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -1508,7 +1505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -1543,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>37</v>
       </c>
@@ -1578,7 +1575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1613,7 +1610,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>43</v>
       </c>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E16F8AD-8827-47EC-A19D-266CFB60DE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533E7357-C497-4F15-9EAE-999C8F966F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -687,10 +687,10 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>BL1 Project Start</t>
-  </si>
-  <si>
-    <t>BL1 Project Finish</t>
+    <t>BL1 Start</t>
+  </si>
+  <si>
+    <t>BL1 Finish</t>
   </si>
 </sst>
 </file>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533E7357-C497-4F15-9EAE-999C8F966F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E49EB17B-148D-4610-8CE2-83749659B514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="215">
   <si>
     <t>Activity ID</t>
   </si>
@@ -429,12 +429,6 @@
     <t>Excavate/ remove existing path and kerb line</t>
   </si>
   <si>
-    <t>AMP8-FLAI-CE-1460</t>
-  </si>
-  <si>
-    <t>Remove hedgerow</t>
-  </si>
-  <si>
     <t>AMP8-FLAI-CE-1400</t>
   </si>
   <si>
@@ -493,12 +487,6 @@
   </si>
   <si>
     <t>Remove TM from Flass Lane and set up on Friars Lane Co-Junction</t>
-  </si>
-  <si>
-    <t>AMP8-FLAI-CE-1290</t>
-  </si>
-  <si>
-    <t>Deveg/Hedgerow removal</t>
   </si>
   <si>
     <t>AMP8-FLAI-CE-1280</t>
@@ -1072,11 +1060,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
-    <col min="2" max="2" width="54" style="1" customWidth="1"/>
+    <col min="2" max="2" width="82.28515625" style="1" customWidth="1"/>
     <col min="3" max="5" width="20" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.28515625" style="3" customWidth="1"/>
     <col min="7" max="7" width="43.28515625" style="2" customWidth="1"/>
@@ -1093,31 +1081,31 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H1" t="s">
         <v>210</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G1" t="s">
-        <v>215</v>
-      </c>
-      <c r="H1" t="s">
-        <v>214</v>
-      </c>
       <c r="I1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="J1" t="s">
+        <v>208</v>
+      </c>
+      <c r="K1" t="s">
         <v>212</v>
-      </c>
-      <c r="K1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3088,25 +3076,25 @@
         <v>132</v>
       </c>
       <c r="C58" s="4">
-        <v>46168.333333333299</v>
+        <v>46112.333333333299</v>
       </c>
       <c r="D58" s="4">
-        <v>46168.708333333299</v>
+        <v>46167.708333333299</v>
       </c>
       <c r="E58" s="4">
-        <v>46143.333333333299</v>
+        <v>46112.333333333299</v>
       </c>
       <c r="F58" s="4">
-        <v>46143.708333333299</v>
+        <v>46142.708333333299</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="H58" t="s">
         <v>4</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>4</v>
@@ -3117,34 +3105,34 @@
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C59" s="4">
-        <v>46112.333333333299</v>
+        <v>46111.333333333299</v>
       </c>
       <c r="D59" s="4">
-        <v>46167.708333333299</v>
+        <v>46111.708333333299</v>
       </c>
       <c r="E59" s="4">
-        <v>46112.333333333299</v>
+        <v>46111.333333333299</v>
       </c>
       <c r="F59" s="4">
-        <v>46142.708333333299</v>
+        <v>46111.708333333299</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="H59" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>135</v>
+        <v>4</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="K59" t="s">
         <v>5</v>
@@ -3158,16 +3146,16 @@
         <v>138</v>
       </c>
       <c r="C60" s="4">
-        <v>46111.333333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="D60" s="4">
-        <v>46111.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="E60" s="4">
-        <v>46111.333333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="F60" s="4">
-        <v>46111.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>4</v>
@@ -3263,13 +3251,13 @@
         <v>144</v>
       </c>
       <c r="C63" s="4">
-        <v>46080.333333333299</v>
+        <v>46076.333333333299</v>
       </c>
       <c r="D63" s="4">
         <v>46080.708333333299</v>
       </c>
       <c r="E63" s="4">
-        <v>46080.333333333299</v>
+        <v>46076.333333333299</v>
       </c>
       <c r="F63" s="4">
         <v>46080.708333333299</v>
@@ -3298,16 +3286,16 @@
         <v>146</v>
       </c>
       <c r="C64" s="4">
-        <v>46076.333333333299</v>
+        <v>46073.333333333299</v>
       </c>
       <c r="D64" s="4">
-        <v>46080.708333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="E64" s="4">
-        <v>46076.333333333299</v>
+        <v>46073.333333333299</v>
       </c>
       <c r="F64" s="4">
-        <v>46080.708333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>4</v>
@@ -3333,13 +3321,13 @@
         <v>148</v>
       </c>
       <c r="C65" s="4">
-        <v>46073.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="D65" s="4">
         <v>46073.708333333299</v>
       </c>
       <c r="E65" s="4">
-        <v>46073.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="F65" s="4">
         <v>46073.708333333299</v>
@@ -3371,13 +3359,13 @@
         <v>46071.333333333299</v>
       </c>
       <c r="D66" s="4">
-        <v>46073.708333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="E66" s="4">
         <v>46071.333333333299</v>
       </c>
       <c r="F66" s="4">
-        <v>46073.708333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>4</v>
@@ -3403,16 +3391,16 @@
         <v>152</v>
       </c>
       <c r="C67" s="4">
-        <v>46071.333333333299</v>
+        <v>46066.333333333299</v>
       </c>
       <c r="D67" s="4">
-        <v>46071.333333333299</v>
+        <v>46071.708333333299</v>
       </c>
       <c r="E67" s="4">
-        <v>46071.333333333299</v>
+        <v>46066.333333333299</v>
       </c>
       <c r="F67" s="4">
-        <v>46071.333333333299</v>
+        <v>46071.708333333299</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>4</v>
@@ -3438,16 +3426,16 @@
         <v>154</v>
       </c>
       <c r="C68" s="4">
-        <v>46069.333333333299</v>
+        <v>46062.333333333299</v>
       </c>
       <c r="D68" s="4">
-        <v>46070.708333333299</v>
+        <v>46065.708333333299</v>
       </c>
       <c r="E68" s="4">
-        <v>46069.333333333299</v>
+        <v>46062.333333333299</v>
       </c>
       <c r="F68" s="4">
-        <v>46070.708333333299</v>
+        <v>46065.708333333299</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>4</v>
@@ -3473,16 +3461,16 @@
         <v>156</v>
       </c>
       <c r="C69" s="4">
-        <v>46066.333333333299</v>
+        <v>46057.333333333299</v>
       </c>
       <c r="D69" s="4">
-        <v>46071.708333333299</v>
+        <v>46062.708333333299</v>
       </c>
       <c r="E69" s="4">
-        <v>46066.333333333299</v>
+        <v>46057.333333333299</v>
       </c>
       <c r="F69" s="4">
-        <v>46071.708333333299</v>
+        <v>46062.708333333299</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>4</v>
@@ -3508,16 +3496,16 @@
         <v>158</v>
       </c>
       <c r="C70" s="4">
-        <v>46062.333333333299</v>
+        <v>46055.333333333299</v>
       </c>
       <c r="D70" s="4">
-        <v>46065.708333333299</v>
+        <v>46055.708333333299</v>
       </c>
       <c r="E70" s="4">
-        <v>46062.333333333299</v>
+        <v>46055.333333333299</v>
       </c>
       <c r="F70" s="4">
-        <v>46065.708333333299</v>
+        <v>46055.708333333299</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>4</v>
@@ -3543,16 +3531,16 @@
         <v>160</v>
       </c>
       <c r="C71" s="4">
-        <v>46057.333333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="D71" s="4">
-        <v>46062.708333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="E71" s="4">
-        <v>46057.333333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="F71" s="4">
-        <v>46062.708333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>4</v>
@@ -3578,16 +3566,16 @@
         <v>162</v>
       </c>
       <c r="C72" s="4">
-        <v>46055.333333333299</v>
+        <v>46051.333333333299</v>
       </c>
       <c r="D72" s="4">
-        <v>46055.708333333299</v>
+        <v>46051.708333333299</v>
       </c>
       <c r="E72" s="4">
-        <v>46055.333333333299</v>
+        <v>46051.333333333299</v>
       </c>
       <c r="F72" s="4">
-        <v>46055.708333333299</v>
+        <v>46051.708333333299</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>4</v>
@@ -3613,16 +3601,16 @@
         <v>164</v>
       </c>
       <c r="C73" s="4">
-        <v>46052.333333333299</v>
+        <v>46050.333333333299</v>
       </c>
       <c r="D73" s="4">
-        <v>46052.333333333299</v>
+        <v>46050.708333333299</v>
       </c>
       <c r="E73" s="4">
-        <v>46052.333333333299</v>
+        <v>46050.333333333299</v>
       </c>
       <c r="F73" s="4">
-        <v>46052.333333333299</v>
+        <v>46050.708333333299</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>4</v>
@@ -3648,16 +3636,16 @@
         <v>166</v>
       </c>
       <c r="C74" s="4">
-        <v>46051.333333333299</v>
+        <v>46050.333333333299</v>
       </c>
       <c r="D74" s="4">
-        <v>46051.708333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="E74" s="4">
-        <v>46051.333333333299</v>
+        <v>46050.333333333299</v>
       </c>
       <c r="F74" s="4">
-        <v>46051.708333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>4</v>
@@ -3683,16 +3671,16 @@
         <v>168</v>
       </c>
       <c r="C75" s="4">
-        <v>46050.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="D75" s="4">
-        <v>46050.708333333299</v>
+        <v>46049.708333333299</v>
       </c>
       <c r="E75" s="4">
-        <v>46050.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="F75" s="4">
-        <v>46050.708333333299</v>
+        <v>46049.708333333299</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>4</v>
@@ -3718,13 +3706,13 @@
         <v>170</v>
       </c>
       <c r="C76" s="4">
-        <v>46050.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="D76" s="4">
         <v>46052.708333333299</v>
       </c>
       <c r="E76" s="4">
-        <v>46050.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="F76" s="4">
         <v>46052.708333333299</v>
@@ -3756,13 +3744,13 @@
         <v>46048.333333333299</v>
       </c>
       <c r="D77" s="4">
-        <v>46049.708333333299</v>
+        <v>46048.708333333299</v>
       </c>
       <c r="E77" s="4">
         <v>46048.333333333299</v>
       </c>
       <c r="F77" s="4">
-        <v>46049.708333333299</v>
+        <v>46048.708333333299</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>4</v>
@@ -3788,16 +3776,16 @@
         <v>174</v>
       </c>
       <c r="C78" s="4">
-        <v>46048.333333333299</v>
+        <v>46045.333333333299</v>
       </c>
       <c r="D78" s="4">
-        <v>46052.708333333299</v>
+        <v>46045.708333333299</v>
       </c>
       <c r="E78" s="4">
-        <v>46048.333333333299</v>
+        <v>46045.333333333299</v>
       </c>
       <c r="F78" s="4">
-        <v>46052.708333333299</v>
+        <v>46045.708333333299</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>4</v>
@@ -3823,16 +3811,16 @@
         <v>176</v>
       </c>
       <c r="C79" s="4">
-        <v>46048.333333333299</v>
+        <v>46044.333333333299</v>
       </c>
       <c r="D79" s="4">
-        <v>46048.708333333299</v>
+        <v>46044.708333333299</v>
       </c>
       <c r="E79" s="4">
-        <v>46048.333333333299</v>
+        <v>46044.333333333299</v>
       </c>
       <c r="F79" s="4">
-        <v>46048.708333333299</v>
+        <v>46044.708333333299</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>4</v>
@@ -3858,16 +3846,16 @@
         <v>178</v>
       </c>
       <c r="C80" s="4">
-        <v>46045.333333333299</v>
+        <v>46043.333333333299</v>
       </c>
       <c r="D80" s="4">
-        <v>46045.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="E80" s="4">
-        <v>46045.333333333299</v>
+        <v>46043.333333333299</v>
       </c>
       <c r="F80" s="4">
-        <v>46045.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>4</v>
@@ -3893,16 +3881,16 @@
         <v>180</v>
       </c>
       <c r="C81" s="4">
-        <v>46044.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="D81" s="4">
-        <v>46044.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="E81" s="4">
-        <v>46044.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="F81" s="4">
-        <v>46044.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>4</v>
@@ -3928,13 +3916,13 @@
         <v>182</v>
       </c>
       <c r="C82" s="4">
-        <v>46043.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="D82" s="4">
         <v>46043.708333333299</v>
       </c>
       <c r="E82" s="4">
-        <v>46043.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="F82" s="4">
         <v>46043.708333333299</v>
@@ -3963,16 +3951,16 @@
         <v>184</v>
       </c>
       <c r="C83" s="4">
-        <v>46042.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="D83" s="4">
-        <v>46043.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="E83" s="4">
-        <v>46042.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="F83" s="4">
-        <v>46043.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>4</v>
@@ -3998,16 +3986,16 @@
         <v>186</v>
       </c>
       <c r="C84" s="4">
-        <v>46042.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="D84" s="4">
-        <v>46043.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="E84" s="4">
-        <v>46042.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="F84" s="4">
-        <v>46043.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>4</v>
@@ -4033,16 +4021,16 @@
         <v>188</v>
       </c>
       <c r="C85" s="4">
-        <v>46041.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="D85" s="4">
-        <v>46041.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="E85" s="4">
-        <v>46041.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="F85" s="4">
-        <v>46041.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>4</v>
@@ -4068,16 +4056,16 @@
         <v>190</v>
       </c>
       <c r="C86" s="4">
-        <v>46041.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="D86" s="4">
-        <v>46041.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="E86" s="4">
-        <v>46041.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="F86" s="4">
-        <v>46041.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>4</v>
@@ -4103,16 +4091,16 @@
         <v>192</v>
       </c>
       <c r="C87" s="4">
-        <v>46038.333333333299</v>
+        <v>46036.333333333299</v>
       </c>
       <c r="D87" s="4">
-        <v>46038.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="E87" s="4">
-        <v>46038.333333333299</v>
+        <v>46036.333333333299</v>
       </c>
       <c r="F87" s="4">
-        <v>46038.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>4</v>
@@ -4138,16 +4126,16 @@
         <v>194</v>
       </c>
       <c r="C88" s="4">
-        <v>46038.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="D88" s="4">
-        <v>46038.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="E88" s="4">
-        <v>46038.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="F88" s="4">
-        <v>46038.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>4</v>
@@ -4173,16 +4161,16 @@
         <v>196</v>
       </c>
       <c r="C89" s="4">
-        <v>46036.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="D89" s="4">
-        <v>46036.708333333299</v>
+        <v>46035.708333333299</v>
       </c>
       <c r="E89" s="4">
-        <v>46036.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="F89" s="4">
-        <v>46036.708333333299</v>
+        <v>46035.708333333299</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>4</v>
@@ -4208,16 +4196,16 @@
         <v>198</v>
       </c>
       <c r="C90" s="4">
-        <v>46035.333333333299</v>
+        <v>46034.333333333299</v>
       </c>
       <c r="D90" s="4">
-        <v>46036.708333333299</v>
+        <v>46034.708333333299</v>
       </c>
       <c r="E90" s="4">
-        <v>46035.333333333299</v>
+        <v>46034.333333333299</v>
       </c>
       <c r="F90" s="4">
-        <v>46036.708333333299</v>
+        <v>46034.708333333299</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>4</v>
@@ -4243,16 +4231,16 @@
         <v>200</v>
       </c>
       <c r="C91" s="4">
-        <v>46035.333333333299</v>
+        <v>46031.333333333299</v>
       </c>
       <c r="D91" s="4">
-        <v>46035.708333333299</v>
+        <v>46031.708333333299</v>
       </c>
       <c r="E91" s="4">
-        <v>46035.333333333299</v>
+        <v>46031.333333333299</v>
       </c>
       <c r="F91" s="4">
-        <v>46035.708333333299</v>
+        <v>46031.708333333299</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>4</v>
@@ -4275,19 +4263,19 @@
         <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="C92" s="4">
-        <v>46034.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="D92" s="4">
-        <v>46034.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="E92" s="4">
-        <v>46034.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="F92" s="4">
-        <v>46034.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>4</v>
@@ -4307,22 +4295,22 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" t="s">
         <v>203</v>
       </c>
-      <c r="B93" t="s">
-        <v>204</v>
-      </c>
       <c r="C93" s="4">
-        <v>46031.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="D93" s="4">
-        <v>46031.708333333299</v>
+        <v>46030.708333333299</v>
       </c>
       <c r="E93" s="4">
-        <v>46031.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="F93" s="4">
-        <v>46031.708333333299</v>
+        <v>46030.708333333299</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>4</v>
@@ -4342,22 +4330,22 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
+        <v>204</v>
+      </c>
+      <c r="B94" t="s">
         <v>205</v>
       </c>
-      <c r="B94" t="s">
-        <v>68</v>
-      </c>
       <c r="C94" s="4">
-        <v>46029.333333333299</v>
+        <v>45947.333333333299</v>
       </c>
       <c r="D94" s="4">
-        <v>46041.708333333299</v>
+        <v>45980.708333333299</v>
       </c>
       <c r="E94" s="4">
-        <v>46029.333333333299</v>
+        <v>45947.333333333299</v>
       </c>
       <c r="F94" s="4">
-        <v>46041.708333333299</v>
+        <v>45980.708333333299</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>4</v>
@@ -4372,76 +4360,6 @@
         <v>13</v>
       </c>
       <c r="K94" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" t="s">
-        <v>206</v>
-      </c>
-      <c r="B95" t="s">
-        <v>207</v>
-      </c>
-      <c r="C95" s="4">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="D95" s="4">
-        <v>46030.708333333299</v>
-      </c>
-      <c r="E95" s="4">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="F95" s="4">
-        <v>46030.708333333299</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H95" t="s">
-        <v>5</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K95" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" t="s">
-        <v>208</v>
-      </c>
-      <c r="B96" t="s">
-        <v>209</v>
-      </c>
-      <c r="C96" s="4">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="D96" s="4">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="E96" s="4">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="F96" s="4">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H96" t="s">
-        <v>5</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K96" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E26048-240A-476B-AE22-507EBFDC768B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7CEB4B-0EA2-4C65-8716-0E77E745D236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TASK" sheetId="1" r:id="rId1"/>
@@ -950,9 +950,6 @@
     <t>Finish</t>
   </si>
   <si>
-    <t>Activity % Complete (%)</t>
-  </si>
-  <si>
     <t>BL Project Start</t>
   </si>
   <si>
@@ -966,6 +963,9 @@
   </si>
   <si>
     <t>Remaining Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity % Complete </t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D1" t="s">
         <v>301</v>
@@ -1366,19 +1366,19 @@
         <v>302</v>
       </c>
       <c r="F1" t="s">
+        <v>308</v>
+      </c>
+      <c r="G1" t="s">
         <v>303</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>304</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>305</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>306</v>
-      </c>
-      <c r="J1" t="s">
-        <v>307</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7CEB4B-0EA2-4C65-8716-0E77E745D236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB45617C-29A7-433F-8CC6-87318EC95C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="309">
   <si>
     <t>Activity ID</t>
   </si>
@@ -2345,8 +2345,8 @@
       <c r="E29" s="2">
         <v>46163.708333333299</v>
       </c>
-      <c r="F29" t="s">
-        <v>5</v>
+      <c r="F29">
+        <v>100</v>
       </c>
       <c r="G29" s="2">
         <v>46154.333333333299</v>

--- a/data/Flass/CL32-FL-March.xlsx
+++ b/data/Flass/CL32-FL-March.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ebenezeramoako\NEW\dm_trackers\data\Flass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB45617C-29A7-433F-8CC6-87318EC95C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6E63EB-BF6A-4DF6-A4BE-8B4C0525D874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="233">
   <si>
     <t>Activity ID</t>
   </si>
@@ -76,12 +76,6 @@
   </si>
   <si>
     <t>Planned Completion</t>
-  </si>
-  <si>
-    <t>AR-FL-KD-1010</t>
-  </si>
-  <si>
-    <t>Team Mobilisation</t>
   </si>
   <si>
     <t>100</t>
@@ -340,235 +334,13 @@
     <t>Shaft level and location confirmation (UU)</t>
   </si>
   <si>
-    <t>AMP8-FLL-PROC-1710</t>
-  </si>
-  <si>
-    <t>HRA</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-PROC-1700</t>
-  </si>
-  <si>
-    <t>Aggregates</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-PROC-1630</t>
-  </si>
-  <si>
-    <t>Traffic management</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-PROC-1610</t>
-  </si>
-  <si>
-    <t>Plate bearing testing</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-PROC-1600</t>
-  </si>
-  <si>
     <t>Hoarding</t>
   </si>
   <si>
-    <t>AMP8-FLL-PROC-1580</t>
-  </si>
-  <si>
-    <t>Soil &amp; drainage</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-MIL-1050</t>
-  </si>
-  <si>
-    <t>Start date lead in/mobilisation</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-MIL-1040</t>
-  </si>
-  <si>
-    <t>Contract Award</t>
-  </si>
-  <si>
     <t>Finish On or After</t>
   </si>
   <si>
-    <t>AMP8-FLL-KD-1160</t>
-  </si>
-  <si>
-    <t>(Completion Date) Early Works Contract</t>
-  </si>
-  <si>
-    <t>Mandatory Finish</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-KD-1030</t>
-  </si>
-  <si>
     <t>-15</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-KD-1020</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-KD-1010</t>
-  </si>
-  <si>
-    <t>Access Date</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-KD-1000</t>
-  </si>
-  <si>
-    <t>Start Date</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1690</t>
-  </si>
-  <si>
-    <t>HRA screening review period (UU)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1680</t>
-  </si>
-  <si>
-    <t>Submit HRA screening report</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1670</t>
-  </si>
-  <si>
-    <t>Produce HRA screening report</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1660</t>
-  </si>
-  <si>
-    <t>TTRO traffic management approval</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1640</t>
-  </si>
-  <si>
-    <t>Produce and submit Streetworks permit (PAA)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1360</t>
-  </si>
-  <si>
-    <t>Consultation with Compliance Officer</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-ECI-1340</t>
-  </si>
-  <si>
-    <t>TTRO Application, Submission and Review period</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1440</t>
-  </si>
-  <si>
-    <t>Client acceptance - construction manager sign off</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1430</t>
-  </si>
-  <si>
-    <t>Construction duration (LOE)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1420</t>
-  </si>
-  <si>
-    <t>Soil strip and import aggregates for Initial compound area</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1410</t>
-  </si>
-  <si>
-    <t>Remove ext fence and install access gate to field</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1350</t>
-  </si>
-  <si>
-    <t>Enabling works TRA - Time Risk Allowance (30% Overall)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1260</t>
-  </si>
-  <si>
-    <t>Plate bearing tests</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1250</t>
-  </si>
-  <si>
-    <t>Aggregates and install piling platform</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1240</t>
-  </si>
-  <si>
-    <t>Import aggregates and construct compound</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1220</t>
-  </si>
-  <si>
-    <t>Cut and fill to level compound</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1210</t>
-  </si>
-  <si>
-    <t>Topsoil strip and stockpile</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1200</t>
-  </si>
-  <si>
-    <t>Site hoarding</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1190</t>
-  </si>
-  <si>
-    <t>Set up temporary fencing</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1180</t>
-  </si>
-  <si>
-    <t>Install cut-off drainage to working area boundary (connection to ext network)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1170</t>
-  </si>
-  <si>
-    <t>Pre-entry soil and drainage survey (main compound)</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-EAW-1110</t>
-  </si>
-  <si>
-    <t>Mobilise to main compound</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-DED-1570</t>
-  </si>
-  <si>
-    <t>Working platform TWD completion milestones</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-DED-1550</t>
-  </si>
-  <si>
-    <t>Hoarding TWD completion milestone</t>
-  </si>
-  <si>
-    <t>AMP8-FLL-DED-1150</t>
-  </si>
-  <si>
-    <t>TRA - Time Risk Allowance (20%)</t>
   </si>
   <si>
     <t>AMP8-FLL-DED-1140</t>
@@ -1339,7 +1111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K139"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.28515625" customWidth="1"/>
@@ -1357,28 +1129,28 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>307</v>
+        <v>231</v>
       </c>
       <c r="D1" t="s">
-        <v>301</v>
+        <v>225</v>
       </c>
       <c r="E1" t="s">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="F1" t="s">
-        <v>308</v>
+        <v>232</v>
       </c>
       <c r="G1" t="s">
-        <v>303</v>
+        <v>227</v>
       </c>
       <c r="H1" t="s">
-        <v>304</v>
+        <v>228</v>
       </c>
       <c r="I1" t="s">
-        <v>305</v>
+        <v>229</v>
       </c>
       <c r="J1" t="s">
-        <v>306</v>
+        <v>230</v>
       </c>
       <c r="K1" t="s">
         <v>2</v>
@@ -1491,28 +1263,28 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="2">
-        <v>46084.333333333299</v>
-      </c>
-      <c r="E5" s="2">
-        <v>46087.708333333299</v>
+        <v>46083.333333333299</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2">
-        <v>46084.333333333299</v>
-      </c>
-      <c r="H5" s="2">
-        <v>46087.708333333299</v>
+        <v>46083.333333333299</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I5" t="s">
         <v>5</v>
@@ -1535,22 +1307,22 @@
         <v>5</v>
       </c>
       <c r="D6" s="2">
-        <v>46083.333333333299</v>
+        <v>46133.333333333299</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2">
-        <v>46083.333333333299</v>
+        <v>46113.333333333299</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I6" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
         <v>6</v>
@@ -1561,10 +1333,10 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -1576,7 +1348,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2">
         <v>46113.333333333299</v>
@@ -1585,7 +1357,7 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
         <v>6</v>
@@ -1605,22 +1377,22 @@
         <v>5</v>
       </c>
       <c r="D8" s="2">
-        <v>46133.333333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2">
-        <v>46113.333333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I8" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="J8" t="s">
         <v>6</v>
@@ -1646,7 +1418,7 @@
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2">
         <v>46083.333333333299</v>
@@ -1681,7 +1453,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G10" s="2">
         <v>46083.333333333299</v>
@@ -1716,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G11" s="2">
         <v>46083.333333333299</v>
@@ -1751,7 +1523,7 @@
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G12" s="2">
         <v>46083.333333333299</v>
@@ -1786,7 +1558,7 @@
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13" s="2">
         <v>46083.333333333299</v>
@@ -1821,7 +1593,7 @@
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2">
         <v>46083.333333333299</v>
@@ -1850,22 +1622,22 @@
         <v>5</v>
       </c>
       <c r="D15" s="2">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>46121.333333333299</v>
+      </c>
+      <c r="E15" s="2">
+        <v>46129.708333333299</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G15" s="2">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>6</v>
+        <v>46107.333333333299</v>
+      </c>
+      <c r="H15" s="2">
+        <v>46119.708333333299</v>
       </c>
       <c r="I15" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="J15" t="s">
         <v>6</v>
@@ -1876,31 +1648,31 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" s="2">
-        <v>46121.333333333299</v>
+        <v>46100.333333333299</v>
       </c>
       <c r="E16" s="2">
-        <v>46129.708333333299</v>
+        <v>46106.708333333299</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G16" s="2">
-        <v>46107.333333333299</v>
+        <v>46100.333333333299</v>
       </c>
       <c r="H16" s="2">
-        <v>46119.708333333299</v>
+        <v>46106.708333333299</v>
       </c>
       <c r="I16" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="J16" t="s">
         <v>6</v>
@@ -1920,16 +1692,16 @@
         <v>5</v>
       </c>
       <c r="D17" s="2">
-        <v>46100.333333333299</v>
+        <v>46097.333333333299</v>
       </c>
       <c r="E17" s="2">
         <v>46106.708333333299</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="2">
-        <v>46100.333333333299</v>
+        <v>46097.333333333299</v>
       </c>
       <c r="H17" s="2">
         <v>46106.708333333299</v>
@@ -1954,20 +1726,20 @@
       <c r="C18" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="2">
         <v>46097.333333333299</v>
       </c>
-      <c r="E18" s="2">
-        <v>46106.708333333299</v>
-      </c>
       <c r="F18" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="2">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18" s="2">
         <v>46097.333333333299</v>
-      </c>
-      <c r="H18" s="2">
-        <v>46106.708333333299</v>
       </c>
       <c r="I18" t="s">
         <v>5</v>
@@ -1989,20 +1761,20 @@
       <c r="C19" t="s">
         <v>5</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>6</v>
+      <c r="D19" s="2">
+        <v>46090.333333333299</v>
       </c>
       <c r="E19" s="2">
-        <v>46097.333333333299</v>
+        <v>46094.708333333299</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G19" s="2">
+        <v>46090.333333333299</v>
       </c>
       <c r="H19" s="2">
-        <v>46097.333333333299</v>
+        <v>46094.708333333299</v>
       </c>
       <c r="I19" t="s">
         <v>5</v>
@@ -2031,7 +1803,7 @@
         <v>46094.708333333299</v>
       </c>
       <c r="F20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="2">
         <v>46090.333333333299</v>
@@ -2060,19 +1832,19 @@
         <v>5</v>
       </c>
       <c r="D21" s="2">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="E21" s="2">
-        <v>46094.708333333299</v>
+        <v>46083.333333333299</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G21" s="2">
-        <v>46090.333333333299</v>
-      </c>
-      <c r="H21" s="2">
-        <v>46094.708333333299</v>
+        <v>46083.333333333299</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I21" t="s">
         <v>5</v>
@@ -2095,22 +1867,22 @@
         <v>5</v>
       </c>
       <c r="D22" s="2">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>46105.333333333299</v>
+      </c>
+      <c r="E22" s="2">
+        <v>46121.708333333299</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="2">
-        <v>46083.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" t="s">
         <v>6</v>
@@ -2127,28 +1899,28 @@
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D23" s="2">
-        <v>46105.333333333299</v>
+        <v>46174.333333333299</v>
       </c>
       <c r="E23" s="2">
-        <v>46121.708333333299</v>
+        <v>46175.708333333299</v>
       </c>
       <c r="F23" t="s">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="G23" s="2">
+        <v>46139.333333333299</v>
+      </c>
+      <c r="H23" s="2">
+        <v>46140.708333333299</v>
       </c>
       <c r="I23" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="J23" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="K23" t="s">
         <v>6</v>
@@ -2156,34 +1928,34 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46141.333333333299</v>
+      </c>
+      <c r="E24" s="2">
+        <v>46171.708333333299</v>
+      </c>
+      <c r="F24" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2">
+        <v>46132.333333333299</v>
+      </c>
+      <c r="H24" s="2">
+        <v>46136.708333333299</v>
+      </c>
+      <c r="I24" t="s">
         <v>56</v>
       </c>
-      <c r="C24" t="s">
+      <c r="J24" t="s">
         <v>57</v>
-      </c>
-      <c r="D24" s="2">
-        <v>46174.333333333299</v>
-      </c>
-      <c r="E24" s="2">
-        <v>46175.708333333299</v>
-      </c>
-      <c r="F24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2">
-        <v>46139.333333333299</v>
-      </c>
-      <c r="H24" s="2">
-        <v>46140.708333333299</v>
-      </c>
-      <c r="I24" t="s">
-        <v>58</v>
-      </c>
-      <c r="J24" t="s">
-        <v>59</v>
       </c>
       <c r="K24" t="s">
         <v>6</v>
@@ -2191,34 +1963,34 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="D25" s="2">
-        <v>46141.333333333299</v>
+        <v>46136.333333333299</v>
       </c>
       <c r="E25" s="2">
-        <v>46171.708333333299</v>
+        <v>46140.708333333299</v>
       </c>
       <c r="F25" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G25" s="2">
-        <v>46132.333333333299</v>
+        <v>46127.333333333299</v>
       </c>
       <c r="H25" s="2">
-        <v>46136.708333333299</v>
+        <v>46129.708333333299</v>
       </c>
       <c r="I25" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="J25" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="K25" t="s">
         <v>6</v>
@@ -2235,19 +2007,19 @@
         <v>5</v>
       </c>
       <c r="D26" s="2">
-        <v>46136.333333333299</v>
+        <v>46129.333333333299</v>
       </c>
       <c r="E26" s="2">
-        <v>46140.708333333299</v>
+        <v>46135.708333333299</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G26" s="2">
-        <v>46127.333333333299</v>
+        <v>46120.333333333299</v>
       </c>
       <c r="H26" s="2">
-        <v>46129.708333333299</v>
+        <v>46126.708333333299</v>
       </c>
       <c r="I26" t="s">
         <v>7</v>
@@ -2269,26 +2041,26 @@
       <c r="C27" t="s">
         <v>5</v>
       </c>
-      <c r="D27" s="2">
-        <v>46129.333333333299</v>
+      <c r="D27" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E27" s="2">
-        <v>46135.708333333299</v>
+        <v>46169.708333333299</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
-      </c>
-      <c r="G27" s="2">
-        <v>46120.333333333299</v>
+        <v>5</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H27" s="2">
-        <v>46126.708333333299</v>
+        <v>46157.708333333299</v>
       </c>
       <c r="I27" t="s">
         <v>7</v>
       </c>
       <c r="J27" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="K27" t="s">
         <v>6</v>
@@ -2296,34 +2068,34 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>6</v>
+        <v>70</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46163.333333333299</v>
       </c>
       <c r="E28" s="2">
-        <v>46169.708333333299</v>
-      </c>
-      <c r="F28" t="s">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>6</v>
+        <v>46163.708333333299</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="G28" s="2">
+        <v>46154.333333333299</v>
       </c>
       <c r="H28" s="2">
-        <v>46157.708333333299</v>
+        <v>46154.708333333299</v>
       </c>
       <c r="I28" t="s">
         <v>7</v>
       </c>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="K28" t="s">
         <v>6</v>
@@ -2331,28 +2103,28 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="D29" s="2">
         <v>46163.333333333299</v>
       </c>
-      <c r="E29" s="2">
-        <v>46163.708333333299</v>
-      </c>
-      <c r="F29">
-        <v>100</v>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>5</v>
       </c>
       <c r="G29" s="2">
         <v>46154.333333333299</v>
       </c>
-      <c r="H29" s="2">
-        <v>46154.708333333299</v>
+      <c r="H29" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I29" t="s">
         <v>7</v>
@@ -2372,28 +2144,28 @@
         <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D30" s="2">
-        <v>46163.333333333299</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>46162.333333333299</v>
+      </c>
+      <c r="E30" s="2">
+        <v>46169.708333333299</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30" s="2">
-        <v>46154.333333333299</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>6</v>
+        <v>46153.333333333299</v>
+      </c>
+      <c r="H30" s="2">
+        <v>46157.708333333299</v>
       </c>
       <c r="I30" t="s">
         <v>7</v>
       </c>
       <c r="J30" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="K30" t="s">
         <v>6</v>
@@ -2410,25 +2182,25 @@
         <v>11</v>
       </c>
       <c r="D31" s="2">
-        <v>46162.333333333299</v>
+        <v>46156.333333333299</v>
       </c>
       <c r="E31" s="2">
-        <v>46169.708333333299</v>
+        <v>46162.708333333299</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31" s="2">
-        <v>46153.333333333299</v>
+        <v>46147.333333333299</v>
       </c>
       <c r="H31" s="2">
-        <v>46157.708333333299</v>
+        <v>46153.708333333299</v>
       </c>
       <c r="I31" t="s">
         <v>7</v>
       </c>
       <c r="J31" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="K31" t="s">
         <v>6</v>
@@ -2445,19 +2217,19 @@
         <v>11</v>
       </c>
       <c r="D32" s="2">
-        <v>46156.333333333299</v>
+        <v>46149.333333333299</v>
       </c>
       <c r="E32" s="2">
-        <v>46162.708333333299</v>
+        <v>46155.708333333299</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
       </c>
       <c r="G32" s="2">
-        <v>46147.333333333299</v>
+        <v>46139.333333333299</v>
       </c>
       <c r="H32" s="2">
-        <v>46153.708333333299</v>
+        <v>46143.708333333299</v>
       </c>
       <c r="I32" t="s">
         <v>7</v>
@@ -2477,22 +2249,22 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="D33" s="2">
-        <v>46149.333333333299</v>
+        <v>46141.333333333299</v>
       </c>
       <c r="E33" s="2">
-        <v>46155.708333333299</v>
+        <v>46148.708333333299</v>
       </c>
       <c r="F33" t="s">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="G33" s="2">
-        <v>46139.333333333299</v>
+        <v>46132.333333333299</v>
       </c>
       <c r="H33" s="2">
-        <v>46143.708333333299</v>
+        <v>46136.708333333299</v>
       </c>
       <c r="I33" t="s">
         <v>7</v>
@@ -2506,34 +2278,34 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D34" s="2">
-        <v>46141.333333333299</v>
+        <v>46129.333333333299</v>
       </c>
       <c r="E34" s="2">
-        <v>46148.708333333299</v>
+        <v>46132.708333333299</v>
       </c>
       <c r="F34" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="G34" s="2">
-        <v>46132.333333333299</v>
+        <v>46120.333333333299</v>
       </c>
       <c r="H34" s="2">
-        <v>46136.708333333299</v>
+        <v>46121.708333333299</v>
       </c>
       <c r="I34" t="s">
         <v>7</v>
       </c>
       <c r="J34" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K34" t="s">
         <v>6</v>
@@ -2550,63 +2322,63 @@
         <v>5</v>
       </c>
       <c r="D35" s="2">
-        <v>46129.333333333299</v>
+        <v>45947.333333333299</v>
       </c>
       <c r="E35" s="2">
-        <v>46132.708333333299</v>
+        <v>45953.708333333299</v>
       </c>
       <c r="F35" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G35" s="2">
-        <v>46120.333333333299</v>
+        <v>45947.333333333299</v>
       </c>
       <c r="H35" s="2">
-        <v>46121.708333333299</v>
+        <v>45953.708333333299</v>
       </c>
       <c r="I35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J35" t="s">
         <v>6</v>
       </c>
       <c r="K35" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="2">
+        <v>45946.708333333299</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="2">
+        <v>45946.708333333299</v>
+      </c>
+      <c r="I36" t="s">
+        <v>5</v>
+      </c>
+      <c r="J36" t="s">
+        <v>6</v>
+      </c>
+      <c r="K36" t="s">
         <v>86</v>
-      </c>
-      <c r="B36" t="s">
-        <v>87</v>
-      </c>
-      <c r="C36" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="2">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E36" s="2">
-        <v>45953.708333333299</v>
-      </c>
-      <c r="F36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G36" s="2">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H36" s="2">
-        <v>45953.708333333299</v>
-      </c>
-      <c r="I36" t="s">
-        <v>5</v>
-      </c>
-      <c r="J36" t="s">
-        <v>6</v>
-      </c>
-      <c r="K36" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2626,7 +2398,7 @@
         <v>45946.708333333299</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>6</v>
@@ -2641,7 +2413,7 @@
         <v>6</v>
       </c>
       <c r="K37" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2654,17 +2426,17 @@
       <c r="C38" t="s">
         <v>5</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>6</v>
+      <c r="D38" s="2">
+        <v>45940.333333333299</v>
       </c>
       <c r="E38" s="2">
         <v>45946.708333333299</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45940.333333333299</v>
       </c>
       <c r="H38" s="2">
         <v>45946.708333333299</v>
@@ -2676,7 +2448,7 @@
         <v>6</v>
       </c>
       <c r="K38" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2689,20 +2461,20 @@
       <c r="C39" t="s">
         <v>5</v>
       </c>
-      <c r="D39" s="2">
-        <v>45940.333333333299</v>
+      <c r="D39" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E39" s="2">
-        <v>45946.708333333299</v>
+        <v>45918.708333333299</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
-      </c>
-      <c r="G39" s="2">
-        <v>45940.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H39" s="2">
-        <v>45946.708333333299</v>
+        <v>45918.708333333299</v>
       </c>
       <c r="I39" t="s">
         <v>5</v>
@@ -2731,7 +2503,7 @@
         <v>45918.708333333299</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>6</v>
@@ -2766,7 +2538,7 @@
         <v>45918.708333333299</v>
       </c>
       <c r="F41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>6</v>
@@ -2786,10 +2558,10 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -2801,7 +2573,7 @@
         <v>45918.708333333299</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>6</v>
@@ -2821,10 +2593,10 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -2833,16 +2605,16 @@
         <v>45919.333333333299</v>
       </c>
       <c r="E43" s="2">
-        <v>45932.708333333299</v>
+        <v>45946.708333333299</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G43" s="2">
         <v>45919.333333333299</v>
       </c>
       <c r="H43" s="2">
-        <v>45932.708333333299</v>
+        <v>45946.708333333299</v>
       </c>
       <c r="I43" t="s">
         <v>5</v>
@@ -2856,28 +2628,28 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B44" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
       </c>
-      <c r="D44" s="2">
-        <v>45919.333333333299</v>
+      <c r="D44" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E44" s="2">
-        <v>45960.708333333299</v>
+        <v>45918.708333333299</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="2">
-        <v>45919.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H44" s="2">
-        <v>45960.708333333299</v>
+        <v>45918.708333333299</v>
       </c>
       <c r="I44" t="s">
         <v>5</v>
@@ -2891,31 +2663,31 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
       </c>
       <c r="D45" s="2">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E45" s="2">
-        <v>45954.708333333299</v>
+        <v>46029.333333333299</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F45" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="2">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H45" s="2">
-        <v>45954.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I45" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J45" t="s">
         <v>6</v>
@@ -2926,63 +2698,63 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B46" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
       </c>
       <c r="D46" s="2">
-        <v>45981.333333333299</v>
-      </c>
-      <c r="E46" s="2">
-        <v>45999.708333333299</v>
+        <v>46029.333333333299</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F46" t="s">
-        <v>16</v>
-      </c>
-      <c r="G46" s="2">
-        <v>45981.333333333299</v>
-      </c>
-      <c r="H46" s="2">
-        <v>45999.708333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I46" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J46" t="s">
         <v>6</v>
       </c>
       <c r="K46" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
       </c>
       <c r="D47" s="2">
-        <v>45919.333333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="E47" s="2">
-        <v>45975.708333333299</v>
+        <v>46090.708333333299</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G47" s="2">
-        <v>45919.333333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="H47" s="2">
-        <v>45975.708333333299</v>
+        <v>46090.708333333299</v>
       </c>
       <c r="I47" t="s">
         <v>5</v>
@@ -2996,34 +2768,34 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C48" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="D48" s="2">
-        <v>45919.333333333299</v>
+        <v>46184.333333333299</v>
       </c>
       <c r="E48" s="2">
-        <v>45936.708333333299</v>
+        <v>46191.708333333299</v>
       </c>
       <c r="F48" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G48" s="2">
-        <v>45919.333333333299</v>
+        <v>46162.333333333299</v>
       </c>
       <c r="H48" s="2">
-        <v>45936.708333333299</v>
+        <v>46170.708333333299</v>
       </c>
       <c r="I48" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J48" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K48" t="s">
         <v>6</v>
@@ -3031,34 +2803,34 @@
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="D49" s="2">
-        <v>45905.333333333299</v>
+        <v>46181.333333333299</v>
       </c>
       <c r="E49" s="2">
-        <v>45918.708333333299</v>
+        <v>46183.708333333299</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G49" s="2">
-        <v>45905.333333333299</v>
+        <v>46157.333333333299</v>
       </c>
       <c r="H49" s="2">
-        <v>45918.708333333299</v>
+        <v>46161.708333333299</v>
       </c>
       <c r="I49" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J49" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" t="s">
         <v>6</v>
@@ -3066,101 +2838,101 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="D50" s="2">
+        <v>46177.333333333299</v>
       </c>
       <c r="E50" s="2">
-        <v>45905.333333333299</v>
+        <v>46178.708333333299</v>
       </c>
       <c r="F50" t="s">
-        <v>16</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="G50" s="2">
+        <v>46155.333333333299</v>
       </c>
       <c r="H50" s="2">
-        <v>45905.333333333299</v>
+        <v>46156.708333333299</v>
       </c>
       <c r="I50" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J50" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K50" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B51" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="D51" s="2">
+        <v>46175.333333333299</v>
       </c>
       <c r="E51" s="2">
-        <v>46136.708333333299</v>
+        <v>46176.708333333299</v>
       </c>
       <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="G51" s="2">
+        <v>46153.333333333299</v>
       </c>
       <c r="H51" s="2">
-        <v>46136.708333333299</v>
+        <v>46154.708333333299</v>
       </c>
       <c r="I51" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J51" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" t="s">
-        <v>120</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D52" s="2">
-        <v>46192.333333333299</v>
+        <v>46171.333333333299</v>
       </c>
       <c r="E52" s="2">
-        <v>46192.333333333299</v>
+        <v>46174.708333333299</v>
       </c>
       <c r="F52" t="s">
         <v>5</v>
       </c>
       <c r="G52" s="2">
-        <v>46171.333333333299</v>
+        <v>46149.333333333299</v>
       </c>
       <c r="H52" s="2">
-        <v>46171.333333333299</v>
+        <v>46150.708333333299</v>
       </c>
       <c r="I52" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="J52" t="s">
         <v>5</v>
@@ -3171,31 +2943,31 @@
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="C53" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>55</v>
+      </c>
+      <c r="D53" s="2">
+        <v>46169.333333333299</v>
       </c>
       <c r="E53" s="2">
-        <v>46191.708333333299</v>
+        <v>46170.708333333299</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
       </c>
-      <c r="G53" s="2" t="s">
-        <v>6</v>
+      <c r="G53" s="2">
+        <v>46147.333333333299</v>
       </c>
       <c r="H53" s="2">
-        <v>46170.708333333299</v>
+        <v>46148.708333333299</v>
       </c>
       <c r="I53" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="J53" t="s">
         <v>5</v>
@@ -3206,34 +2978,34 @@
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B54" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C54" t="s">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="D54" s="2">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
+        <v>46168.333333333299</v>
+      </c>
+      <c r="E54" s="2">
+        <v>46168.708333333299</v>
       </c>
       <c r="F54" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G54" s="2">
-        <v>45919.333333333299</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>6</v>
+        <v>46143.333333333299</v>
+      </c>
+      <c r="H54" s="2">
+        <v>46143.708333333299</v>
       </c>
       <c r="I54" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J54" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K54" t="s">
         <v>6</v>
@@ -3241,34 +3013,34 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
       </c>
       <c r="D55" s="2">
-        <v>45905.333333333299</v>
+        <v>46168.333333333299</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G55" s="2">
-        <v>45905.333333333299</v>
+        <v>46143.333333333299</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I55" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J55" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K55" t="s">
         <v>6</v>
@@ -3276,34 +3048,34 @@
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B56" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
       </c>
       <c r="D56" s="2">
-        <v>45950.333333333299</v>
-      </c>
-      <c r="E56" s="2">
-        <v>45953.708333333299</v>
+        <v>46168.333333333299</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F56" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G56" s="2">
-        <v>45950.333333333299</v>
-      </c>
-      <c r="H56" s="2">
-        <v>45953.708333333299</v>
+        <v>46143.333333333299</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I56" t="s">
-        <v>5</v>
+        <v>101</v>
       </c>
       <c r="J56" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" t="s">
         <v>6</v>
@@ -3311,10 +3083,10 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -3323,16 +3095,16 @@
         <v>6</v>
       </c>
       <c r="E57" s="2">
-        <v>45953.708333333299</v>
+        <v>46091.708333333299</v>
       </c>
       <c r="F57" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H57" s="2">
-        <v>45953.708333333299</v>
+        <v>46091.708333333299</v>
       </c>
       <c r="I57" t="s">
         <v>5</v>
@@ -3341,33 +3113,33 @@
         <v>6</v>
       </c>
       <c r="K57" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
       </c>
-      <c r="D58" s="2">
-        <v>45933.333333333299</v>
+      <c r="D58" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E58" s="2">
-        <v>45947.708333333299</v>
+        <v>46090.708333333299</v>
       </c>
       <c r="F58" t="s">
-        <v>16</v>
-      </c>
-      <c r="G58" s="2">
-        <v>45933.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H58" s="2">
-        <v>45947.708333333299</v>
+        <v>46090.708333333299</v>
       </c>
       <c r="I58" t="s">
         <v>5</v>
@@ -3376,39 +3148,39 @@
         <v>6</v>
       </c>
       <c r="K58" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
+        <v>139</v>
+      </c>
+      <c r="D59" s="2">
+        <v>46112.333333333299</v>
       </c>
       <c r="E59" s="2">
-        <v>45947.708333333299</v>
+        <v>46167.708333333299</v>
       </c>
       <c r="F59" t="s">
-        <v>16</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="G59" s="2">
+        <v>46112.333333333299</v>
       </c>
       <c r="H59" s="2">
-        <v>45947.708333333299</v>
+        <v>46142.708333333299</v>
       </c>
       <c r="I59" t="s">
-        <v>5</v>
+        <v>140</v>
       </c>
       <c r="J59" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K59" t="s">
         <v>6</v>
@@ -3416,28 +3188,28 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B60" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
       </c>
       <c r="D60" s="2">
-        <v>45919.333333333299</v>
+        <v>46111.333333333299</v>
       </c>
       <c r="E60" s="2">
-        <v>45947.708333333299</v>
+        <v>46111.708333333299</v>
       </c>
       <c r="F60" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G60" s="2">
-        <v>45919.333333333299</v>
+        <v>46111.333333333299</v>
       </c>
       <c r="H60" s="2">
-        <v>45947.708333333299</v>
+        <v>46111.708333333299</v>
       </c>
       <c r="I60" t="s">
         <v>5</v>
@@ -3451,10 +3223,10 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B61" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -3463,22 +3235,22 @@
         <v>6</v>
       </c>
       <c r="E61" s="2">
-        <v>45947.708333333299</v>
+        <v>46168.333333333299</v>
       </c>
       <c r="F61" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H61" s="2">
-        <v>45947.708333333299</v>
+        <v>46113.333333333299</v>
       </c>
       <c r="I61" t="s">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="J61" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="K61" t="s">
         <v>6</v>
@@ -3486,28 +3258,28 @@
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B62" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
       </c>
-      <c r="D62" s="2">
-        <v>45919.333333333299</v>
+      <c r="D62" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E62" s="2">
-        <v>45947.708333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="F62" t="s">
-        <v>16</v>
-      </c>
-      <c r="G62" s="2">
-        <v>45919.333333333299</v>
+        <v>14</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="H62" s="2">
-        <v>45947.708333333299</v>
+        <v>46083.333333333299</v>
       </c>
       <c r="I62" t="s">
         <v>5</v>
@@ -3516,39 +3288,39 @@
         <v>6</v>
       </c>
       <c r="K62" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B63" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
+      <c r="D63" s="2">
+        <v>46080.333333333299</v>
       </c>
       <c r="E63" s="2">
-        <v>46191.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="F63" t="s">
-        <v>5</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G63" s="2">
+        <v>46080.333333333299</v>
       </c>
       <c r="H63" s="2">
-        <v>46170.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="I63" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J63" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K63" t="s">
         <v>6</v>
@@ -3556,28 +3328,28 @@
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
       </c>
       <c r="D64" s="2">
-        <v>45957.708333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="E64" s="2">
-        <v>46010.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="F64" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G64" s="2">
-        <v>45957.708333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="H64" s="2">
-        <v>46010.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="I64" t="s">
         <v>5</v>
@@ -3591,28 +3363,28 @@
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B65" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
       </c>
       <c r="D65" s="2">
-        <v>45965.333333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="E65" s="2">
-        <v>45974.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="F65" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G65" s="2">
-        <v>45965.333333333299</v>
+        <v>46080.333333333299</v>
       </c>
       <c r="H65" s="2">
-        <v>45974.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="I65" t="s">
         <v>5</v>
@@ -3626,28 +3398,28 @@
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B66" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
       </c>
       <c r="D66" s="2">
-        <v>45958.333333333299</v>
+        <v>46076.333333333299</v>
       </c>
       <c r="E66" s="2">
-        <v>45960.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G66" s="2">
-        <v>45958.333333333299</v>
+        <v>46076.333333333299</v>
       </c>
       <c r="H66" s="2">
-        <v>45960.708333333299</v>
+        <v>46080.708333333299</v>
       </c>
       <c r="I66" t="s">
         <v>5</v>
@@ -3661,28 +3433,28 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B67" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
       </c>
       <c r="D67" s="2">
-        <v>46010.333333333299</v>
+        <v>46073.333333333299</v>
       </c>
       <c r="E67" s="2">
-        <v>46010.333333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G67" s="2">
-        <v>46010.333333333299</v>
+        <v>46073.333333333299</v>
       </c>
       <c r="H67" s="2">
-        <v>46010.333333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="I67" t="s">
         <v>5</v>
@@ -3696,28 +3468,28 @@
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B68" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
       </c>
       <c r="D68" s="2">
-        <v>46000.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="E68" s="2">
-        <v>46002.708333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="F68" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G68" s="2">
-        <v>46000.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="H68" s="2">
-        <v>46002.708333333299</v>
+        <v>46073.708333333299</v>
       </c>
       <c r="I68" t="s">
         <v>5</v>
@@ -3731,28 +3503,28 @@
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
       </c>
       <c r="D69" s="2">
-        <v>45992.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="E69" s="2">
-        <v>45996.708333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G69" s="2">
-        <v>45992.333333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="H69" s="2">
-        <v>45996.708333333299</v>
+        <v>46071.333333333299</v>
       </c>
       <c r="I69" t="s">
         <v>5</v>
@@ -3766,28 +3538,28 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="2">
-        <v>45974.333333333299</v>
+        <v>46069.333333333299</v>
       </c>
       <c r="E70" s="2">
-        <v>45989.708333333299</v>
+        <v>46070.708333333299</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G70" s="2">
-        <v>45974.333333333299</v>
+        <v>46069.333333333299</v>
       </c>
       <c r="H70" s="2">
-        <v>45989.708333333299</v>
+        <v>46070.708333333299</v>
       </c>
       <c r="I70" t="s">
         <v>5</v>
@@ -3801,28 +3573,28 @@
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
       </c>
       <c r="D71" s="2">
-        <v>45980.333333333299</v>
+        <v>46066.333333333299</v>
       </c>
       <c r="E71" s="2">
-        <v>45989.708333333299</v>
+        <v>46071.708333333299</v>
       </c>
       <c r="F71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G71" s="2">
-        <v>45980.333333333299</v>
+        <v>46066.333333333299</v>
       </c>
       <c r="H71" s="2">
-        <v>45989.708333333299</v>
+        <v>46071.708333333299</v>
       </c>
       <c r="I71" t="s">
         <v>5</v>
@@ -3836,28 +3608,28 @@
     </row>
     <row r="72" spans="1:11">
       <c r="A72" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
       </c>
       <c r="D72" s="2">
-        <v>45972.333333333299</v>
+        <v>46062.333333333299</v>
       </c>
       <c r="E72" s="2">
-        <v>45975.333333333299</v>
+        <v>46065.708333333299</v>
       </c>
       <c r="F72" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G72" s="2">
-        <v>45972.333333333299</v>
+        <v>46062.333333333299</v>
       </c>
       <c r="H72" s="2">
-        <v>45975.333333333299</v>
+        <v>46065.708333333299</v>
       </c>
       <c r="I72" t="s">
         <v>5</v>
@@ -3871,28 +3643,28 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B73" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
       </c>
       <c r="D73" s="2">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="E73" s="2">
-        <v>46010.708333333299</v>
+        <v>46062.333333333299</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F73" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G73" s="2">
-        <v>45992.333333333299</v>
-      </c>
-      <c r="H73" s="2">
-        <v>46010.708333333299</v>
+        <v>46062.333333333299</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I73" t="s">
         <v>5</v>
@@ -3906,28 +3678,28 @@
     </row>
     <row r="74" spans="1:11">
       <c r="A74" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="B74" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
       </c>
       <c r="D74" s="2">
-        <v>45964.333333333299</v>
+        <v>46057.333333333299</v>
       </c>
       <c r="E74" s="2">
-        <v>45966.708333333299</v>
+        <v>46062.708333333299</v>
       </c>
       <c r="F74" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G74" s="2">
-        <v>45964.333333333299</v>
+        <v>46057.333333333299</v>
       </c>
       <c r="H74" s="2">
-        <v>45966.708333333299</v>
+        <v>46062.708333333299</v>
       </c>
       <c r="I74" t="s">
         <v>5</v>
@@ -3941,28 +3713,28 @@
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
       </c>
       <c r="D75" s="2">
-        <v>45978.333333333299</v>
+        <v>46055.333333333299</v>
       </c>
       <c r="E75" s="2">
-        <v>45988.708333333299</v>
+        <v>46055.708333333299</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G75" s="2">
-        <v>45978.333333333299</v>
+        <v>46055.333333333299</v>
       </c>
       <c r="H75" s="2">
-        <v>45988.708333333299</v>
+        <v>46055.708333333299</v>
       </c>
       <c r="I75" t="s">
         <v>5</v>
@@ -3976,28 +3748,28 @@
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B76" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
       </c>
       <c r="D76" s="2">
-        <v>45937.333333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="E76" s="2">
-        <v>45943.708333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="F76" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G76" s="2">
-        <v>45937.333333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="H76" s="2">
-        <v>45943.708333333299</v>
+        <v>46052.333333333299</v>
       </c>
       <c r="I76" t="s">
         <v>5</v>
@@ -4011,28 +3783,28 @@
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
       </c>
       <c r="D77" s="2">
-        <v>45957.333333333299</v>
+        <v>46051.333333333299</v>
       </c>
       <c r="E77" s="2">
-        <v>45957.708333333299</v>
+        <v>46051.708333333299</v>
       </c>
       <c r="F77" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G77" s="2">
-        <v>45957.333333333299</v>
+        <v>46051.333333333299</v>
       </c>
       <c r="H77" s="2">
-        <v>45957.708333333299</v>
+        <v>46051.708333333299</v>
       </c>
       <c r="I77" t="s">
         <v>5</v>
@@ -4046,28 +3818,28 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B78" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>6</v>
+      <c r="D78" s="2">
+        <v>46050.333333333299</v>
       </c>
       <c r="E78" s="2">
-        <v>45947.333333333299</v>
+        <v>46050.708333333299</v>
       </c>
       <c r="F78" t="s">
-        <v>16</v>
-      </c>
-      <c r="G78" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G78" s="2">
+        <v>46050.333333333299</v>
       </c>
       <c r="H78" s="2">
-        <v>45947.333333333299</v>
+        <v>46050.708333333299</v>
       </c>
       <c r="I78" t="s">
         <v>5</v>
@@ -4081,28 +3853,28 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B79" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>6</v>
+      <c r="D79" s="2">
+        <v>46050.333333333299</v>
       </c>
       <c r="E79" s="2">
-        <v>45947.333333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="F79" t="s">
-        <v>16</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G79" s="2">
+        <v>46050.333333333299</v>
       </c>
       <c r="H79" s="2">
-        <v>45947.333333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="I79" t="s">
         <v>5</v>
@@ -4116,28 +3888,28 @@
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B80" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
       </c>
       <c r="D80" s="2">
-        <v>45947.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="E80" s="2">
-        <v>45947.333333333299</v>
+        <v>46049.708333333299</v>
       </c>
       <c r="F80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G80" s="2">
-        <v>45947.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="H80" s="2">
-        <v>45947.333333333299</v>
+        <v>46049.708333333299</v>
       </c>
       <c r="I80" t="s">
         <v>5</v>
@@ -4151,28 +3923,28 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>6</v>
+      <c r="D81" s="2">
+        <v>46048.333333333299</v>
       </c>
       <c r="E81" s="2">
-        <v>45918.708333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="F81" t="s">
-        <v>16</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G81" s="2">
+        <v>46048.333333333299</v>
       </c>
       <c r="H81" s="2">
-        <v>45918.708333333299</v>
+        <v>46052.708333333299</v>
       </c>
       <c r="I81" t="s">
         <v>5</v>
@@ -4186,28 +3958,28 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B82" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
       </c>
       <c r="D82" s="2">
-        <v>45919.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="E82" s="2">
-        <v>45946.708333333299</v>
+        <v>46048.708333333299</v>
       </c>
       <c r="F82" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G82" s="2">
-        <v>45919.333333333299</v>
+        <v>46048.333333333299</v>
       </c>
       <c r="H82" s="2">
-        <v>45946.708333333299</v>
+        <v>46048.708333333299</v>
       </c>
       <c r="I82" t="s">
         <v>5</v>
@@ -4221,28 +3993,28 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>6</v>
+      <c r="D83" s="2">
+        <v>46045.333333333299</v>
       </c>
       <c r="E83" s="2">
-        <v>45918.708333333299</v>
+        <v>46045.708333333299</v>
       </c>
       <c r="F83" t="s">
-        <v>16</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G83" s="2">
+        <v>46045.333333333299</v>
       </c>
       <c r="H83" s="2">
-        <v>45918.708333333299</v>
+        <v>46045.708333333299</v>
       </c>
       <c r="I83" t="s">
         <v>5</v>
@@ -4256,31 +4028,31 @@
     </row>
     <row r="84" spans="1:11">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B84" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>6</v>
+        <v>46044.333333333299</v>
+      </c>
+      <c r="E84" s="2">
+        <v>46044.708333333299</v>
       </c>
       <c r="F84" t="s">
-        <v>16</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G84" s="2">
+        <v>46044.333333333299</v>
+      </c>
+      <c r="H84" s="2">
+        <v>46044.708333333299</v>
       </c>
       <c r="I84" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J84" t="s">
         <v>6</v>
@@ -4291,31 +4063,31 @@
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
       </c>
       <c r="D85" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>6</v>
+        <v>46043.333333333299</v>
+      </c>
+      <c r="E85" s="2">
+        <v>46043.708333333299</v>
       </c>
       <c r="F85" t="s">
-        <v>16</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G85" s="2">
+        <v>46043.333333333299</v>
+      </c>
+      <c r="H85" s="2">
+        <v>46043.708333333299</v>
       </c>
       <c r="I85" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J85" t="s">
         <v>6</v>
@@ -4326,28 +4098,28 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
       </c>
       <c r="D86" s="2">
-        <v>46083.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="E86" s="2">
-        <v>46090.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="F86" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G86" s="2">
-        <v>46083.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="H86" s="2">
-        <v>46090.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="I86" t="s">
         <v>5</v>
@@ -4361,34 +4133,34 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C87" t="s">
-        <v>191</v>
+        <v>5</v>
       </c>
       <c r="D87" s="2">
-        <v>46184.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="E87" s="2">
-        <v>46191.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="F87" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G87" s="2">
-        <v>46162.333333333299</v>
+        <v>46042.333333333299</v>
       </c>
       <c r="H87" s="2">
-        <v>46170.708333333299</v>
+        <v>46043.708333333299</v>
       </c>
       <c r="I87" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J87" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K87" t="s">
         <v>6</v>
@@ -4396,34 +4168,34 @@
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B88" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C88" t="s">
-        <v>194</v>
+        <v>5</v>
       </c>
       <c r="D88" s="2">
-        <v>46181.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="E88" s="2">
-        <v>46183.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="F88" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G88" s="2">
-        <v>46157.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="H88" s="2">
-        <v>46161.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="I88" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J88" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K88" t="s">
         <v>6</v>
@@ -4431,34 +4203,34 @@
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C89" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D89" s="2">
-        <v>46177.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="E89" s="2">
-        <v>46178.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="F89" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G89" s="2">
-        <v>46155.333333333299</v>
+        <v>46041.333333333299</v>
       </c>
       <c r="H89" s="2">
-        <v>46156.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="I89" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J89" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K89" t="s">
         <v>6</v>
@@ -4466,34 +4238,34 @@
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B90" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C90" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D90" s="2">
-        <v>46175.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="E90" s="2">
-        <v>46176.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="F90" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G90" s="2">
-        <v>46153.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="H90" s="2">
-        <v>46154.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="I90" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J90" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" t="s">
         <v>6</v>
@@ -4501,34 +4273,34 @@
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C91" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D91" s="2">
-        <v>46171.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="E91" s="2">
-        <v>46174.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="F91" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G91" s="2">
-        <v>46149.333333333299</v>
+        <v>46038.333333333299</v>
       </c>
       <c r="H91" s="2">
-        <v>46150.708333333299</v>
+        <v>46038.708333333299</v>
       </c>
       <c r="I91" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J91" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K91" t="s">
         <v>6</v>
@@ -4536,34 +4308,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B92" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C92" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D92" s="2">
-        <v>46169.333333333299</v>
+        <v>46036.333333333299</v>
       </c>
       <c r="E92" s="2">
-        <v>46170.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="F92" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G92" s="2">
-        <v>46147.333333333299</v>
+        <v>46036.333333333299</v>
       </c>
       <c r="H92" s="2">
-        <v>46148.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="I92" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J92" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K92" t="s">
         <v>6</v>
@@ -4571,34 +4343,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B93" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C93" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="D93" s="2">
-        <v>46168.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="E93" s="2">
-        <v>46168.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="F93" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G93" s="2">
-        <v>46143.333333333299</v>
+        <v>46035.333333333299</v>
       </c>
       <c r="H93" s="2">
-        <v>46143.708333333299</v>
+        <v>46036.708333333299</v>
       </c>
       <c r="I93" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J93" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K93" t="s">
         <v>6</v>
@@ -4606,34 +4378,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="B94" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C94" t="s">
         <v>5</v>
       </c>
       <c r="D94" s="2">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>6</v>
+        <v>46035.333333333299</v>
+      </c>
+      <c r="E94" s="2">
+        <v>46035.708333333299</v>
       </c>
       <c r="F94" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G94" s="2">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>6</v>
+        <v>46035.333333333299</v>
+      </c>
+      <c r="H94" s="2">
+        <v>46035.708333333299</v>
       </c>
       <c r="I94" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J94" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K94" t="s">
         <v>6</v>
@@ -4641,34 +4413,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B95" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C95" t="s">
         <v>5</v>
       </c>
       <c r="D95" s="2">
-        <v>46168.333333333299</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>6</v>
+        <v>46034.333333333299</v>
+      </c>
+      <c r="E95" s="2">
+        <v>46034.708333333299</v>
       </c>
       <c r="F95" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G95" s="2">
-        <v>46143.333333333299</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>6</v>
+        <v>46034.333333333299</v>
+      </c>
+      <c r="H95" s="2">
+        <v>46034.708333333299</v>
       </c>
       <c r="I95" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="J95" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K95" t="s">
         <v>6</v>
@@ -4676,28 +4448,28 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B96" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C96" t="s">
         <v>5</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>6</v>
+      <c r="D96" s="2">
+        <v>46031.333333333299</v>
       </c>
       <c r="E96" s="2">
-        <v>46091.708333333299</v>
+        <v>46031.708333333299</v>
       </c>
       <c r="F96" t="s">
-        <v>16</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G96" s="2">
+        <v>46031.333333333299</v>
       </c>
       <c r="H96" s="2">
-        <v>46091.708333333299</v>
+        <v>46031.708333333299</v>
       </c>
       <c r="I96" t="s">
         <v>5</v>
@@ -4706,33 +4478,33 @@
         <v>6</v>
       </c>
       <c r="K96" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B97" t="s">
-        <v>212</v>
+        <v>99</v>
       </c>
       <c r="C97" t="s">
         <v>5</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>6</v>
+      <c r="D97" s="2">
+        <v>46029.333333333299</v>
       </c>
       <c r="E97" s="2">
-        <v>46090.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="F97" t="s">
-        <v>16</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G97" s="2">
+        <v>46029.333333333299</v>
       </c>
       <c r="H97" s="2">
-        <v>46090.708333333299</v>
+        <v>46041.708333333299</v>
       </c>
       <c r="I97" t="s">
         <v>5</v>
@@ -4741,39 +4513,39 @@
         <v>6</v>
       </c>
       <c r="K97" t="s">
-        <v>117</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B98" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C98" t="s">
-        <v>215</v>
+        <v>5</v>
       </c>
       <c r="D98" s="2">
-        <v>46112.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="E98" s="2">
-        <v>46167.708333333299</v>
+        <v>46030.708333333299</v>
       </c>
       <c r="F98" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G98" s="2">
-        <v>46112.333333333299</v>
+        <v>46029.333333333299</v>
       </c>
       <c r="H98" s="2">
-        <v>46142.708333333299</v>
+        <v>46030.708333333299</v>
       </c>
       <c r="I98" t="s">
-        <v>216</v>
+        <v>5</v>
       </c>
       <c r="J98" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K98" t="s">
         <v>6</v>
@@ -4781,28 +4553,28 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B99" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="C99" t="s">
         <v>5</v>
       </c>
       <c r="D99" s="2">
-        <v>46111.333333333299</v>
-      </c>
-      <c r="E99" s="2">
-        <v>46111.708333333299</v>
+        <v>46029.333333333299</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="F99" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G99" s="2">
-        <v>46111.333333333299</v>
-      </c>
-      <c r="H99" s="2">
-        <v>46111.708333333299</v>
+        <v>46029.333333333299</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="I99" t="s">
         <v>5</v>
@@ -4816,1401 +4588,36 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B100" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
       </c>
-      <c r="D100" s="2" t="s">
-        <v>6</v>
+      <c r="D100" s="2">
+        <v>45947.333333333299</v>
       </c>
       <c r="E100" s="2">
-        <v>46168.333333333299</v>
+        <v>45980.708333333299</v>
       </c>
       <c r="F100" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="G100" s="2">
+        <v>45947.333333333299</v>
       </c>
       <c r="H100" s="2">
-        <v>46113.333333333299</v>
+        <v>45980.708333333299</v>
       </c>
       <c r="I100" t="s">
-        <v>221</v>
+        <v>5</v>
       </c>
       <c r="J100" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="K100" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" t="s">
-        <v>222</v>
-      </c>
-      <c r="B101" t="s">
-        <v>223</v>
-      </c>
-      <c r="C101" t="s">
-        <v>5</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E101" s="2">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="F101" t="s">
-        <v>16</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H101" s="2">
-        <v>46083.333333333299</v>
-      </c>
-      <c r="I101" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" t="s">
-        <v>6</v>
-      </c>
-      <c r="K101" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" t="s">
-        <v>224</v>
-      </c>
-      <c r="B102" t="s">
-        <v>225</v>
-      </c>
-      <c r="C102" t="s">
-        <v>5</v>
-      </c>
-      <c r="D102" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="E102" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="F102" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H102" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="I102" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" t="s">
-        <v>6</v>
-      </c>
-      <c r="K102" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="A103" t="s">
-        <v>226</v>
-      </c>
-      <c r="B103" t="s">
-        <v>227</v>
-      </c>
-      <c r="C103" t="s">
-        <v>5</v>
-      </c>
-      <c r="D103" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="E103" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="F103" t="s">
-        <v>16</v>
-      </c>
-      <c r="G103" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H103" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="I103" t="s">
-        <v>5</v>
-      </c>
-      <c r="J103" t="s">
-        <v>6</v>
-      </c>
-      <c r="K103" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" t="s">
-        <v>228</v>
-      </c>
-      <c r="B104" t="s">
-        <v>229</v>
-      </c>
-      <c r="C104" t="s">
-        <v>5</v>
-      </c>
-      <c r="D104" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="E104" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="F104" t="s">
-        <v>16</v>
-      </c>
-      <c r="G104" s="2">
-        <v>46080.333333333299</v>
-      </c>
-      <c r="H104" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="I104" t="s">
-        <v>5</v>
-      </c>
-      <c r="J104" t="s">
-        <v>6</v>
-      </c>
-      <c r="K104" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
-      <c r="A105" t="s">
-        <v>230</v>
-      </c>
-      <c r="B105" t="s">
-        <v>231</v>
-      </c>
-      <c r="C105" t="s">
-        <v>5</v>
-      </c>
-      <c r="D105" s="2">
-        <v>46076.333333333299</v>
-      </c>
-      <c r="E105" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="F105" t="s">
-        <v>16</v>
-      </c>
-      <c r="G105" s="2">
-        <v>46076.333333333299</v>
-      </c>
-      <c r="H105" s="2">
-        <v>46080.708333333299</v>
-      </c>
-      <c r="I105" t="s">
-        <v>5</v>
-      </c>
-      <c r="J105" t="s">
-        <v>6</v>
-      </c>
-      <c r="K105" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" t="s">
-        <v>232</v>
-      </c>
-      <c r="B106" t="s">
-        <v>233</v>
-      </c>
-      <c r="C106" t="s">
-        <v>5</v>
-      </c>
-      <c r="D106" s="2">
-        <v>46073.333333333299</v>
-      </c>
-      <c r="E106" s="2">
-        <v>46073.708333333299</v>
-      </c>
-      <c r="F106" t="s">
-        <v>16</v>
-      </c>
-      <c r="G106" s="2">
-        <v>46073.333333333299</v>
-      </c>
-      <c r="H106" s="2">
-        <v>46073.708333333299</v>
-      </c>
-      <c r="I106" t="s">
-        <v>5</v>
-      </c>
-      <c r="J106" t="s">
-        <v>6</v>
-      </c>
-      <c r="K106" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
-      <c r="A107" t="s">
-        <v>234</v>
-      </c>
-      <c r="B107" t="s">
-        <v>235</v>
-      </c>
-      <c r="C107" t="s">
-        <v>5</v>
-      </c>
-      <c r="D107" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="E107" s="2">
-        <v>46073.708333333299</v>
-      </c>
-      <c r="F107" t="s">
-        <v>16</v>
-      </c>
-      <c r="G107" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="H107" s="2">
-        <v>46073.708333333299</v>
-      </c>
-      <c r="I107" t="s">
-        <v>5</v>
-      </c>
-      <c r="J107" t="s">
-        <v>6</v>
-      </c>
-      <c r="K107" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" t="s">
-        <v>236</v>
-      </c>
-      <c r="B108" t="s">
-        <v>237</v>
-      </c>
-      <c r="C108" t="s">
-        <v>5</v>
-      </c>
-      <c r="D108" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="E108" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="F108" t="s">
-        <v>16</v>
-      </c>
-      <c r="G108" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="H108" s="2">
-        <v>46071.333333333299</v>
-      </c>
-      <c r="I108" t="s">
-        <v>5</v>
-      </c>
-      <c r="J108" t="s">
-        <v>6</v>
-      </c>
-      <c r="K108" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" t="s">
-        <v>238</v>
-      </c>
-      <c r="B109" t="s">
-        <v>239</v>
-      </c>
-      <c r="C109" t="s">
-        <v>5</v>
-      </c>
-      <c r="D109" s="2">
-        <v>46069.333333333299</v>
-      </c>
-      <c r="E109" s="2">
-        <v>46070.708333333299</v>
-      </c>
-      <c r="F109" t="s">
-        <v>16</v>
-      </c>
-      <c r="G109" s="2">
-        <v>46069.333333333299</v>
-      </c>
-      <c r="H109" s="2">
-        <v>46070.708333333299</v>
-      </c>
-      <c r="I109" t="s">
-        <v>5</v>
-      </c>
-      <c r="J109" t="s">
-        <v>6</v>
-      </c>
-      <c r="K109" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="A110" t="s">
-        <v>240</v>
-      </c>
-      <c r="B110" t="s">
-        <v>241</v>
-      </c>
-      <c r="C110" t="s">
-        <v>5</v>
-      </c>
-      <c r="D110" s="2">
-        <v>46066.333333333299</v>
-      </c>
-      <c r="E110" s="2">
-        <v>46071.708333333299</v>
-      </c>
-      <c r="F110" t="s">
-        <v>16</v>
-      </c>
-      <c r="G110" s="2">
-        <v>46066.333333333299</v>
-      </c>
-      <c r="H110" s="2">
-        <v>46071.708333333299</v>
-      </c>
-      <c r="I110" t="s">
-        <v>5</v>
-      </c>
-      <c r="J110" t="s">
-        <v>6</v>
-      </c>
-      <c r="K110" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" t="s">
-        <v>242</v>
-      </c>
-      <c r="B111" t="s">
-        <v>243</v>
-      </c>
-      <c r="C111" t="s">
-        <v>5</v>
-      </c>
-      <c r="D111" s="2">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="E111" s="2">
-        <v>46065.708333333299</v>
-      </c>
-      <c r="F111" t="s">
-        <v>16</v>
-      </c>
-      <c r="G111" s="2">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="H111" s="2">
-        <v>46065.708333333299</v>
-      </c>
-      <c r="I111" t="s">
-        <v>5</v>
-      </c>
-      <c r="J111" t="s">
-        <v>6</v>
-      </c>
-      <c r="K111" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" t="s">
-        <v>244</v>
-      </c>
-      <c r="B112" t="s">
-        <v>245</v>
-      </c>
-      <c r="C112" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="2">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F112" t="s">
-        <v>16</v>
-      </c>
-      <c r="G112" s="2">
-        <v>46062.333333333299</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I112" t="s">
-        <v>5</v>
-      </c>
-      <c r="J112" t="s">
-        <v>6</v>
-      </c>
-      <c r="K112" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
-      <c r="A113" t="s">
-        <v>246</v>
-      </c>
-      <c r="B113" t="s">
-        <v>247</v>
-      </c>
-      <c r="C113" t="s">
-        <v>5</v>
-      </c>
-      <c r="D113" s="2">
-        <v>46057.333333333299</v>
-      </c>
-      <c r="E113" s="2">
-        <v>46062.708333333299</v>
-      </c>
-      <c r="F113" t="s">
-        <v>16</v>
-      </c>
-      <c r="G113" s="2">
-        <v>46057.333333333299</v>
-      </c>
-      <c r="H113" s="2">
-        <v>46062.708333333299</v>
-      </c>
-      <c r="I113" t="s">
-        <v>5</v>
-      </c>
-      <c r="J113" t="s">
-        <v>6</v>
-      </c>
-      <c r="K113" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
-      <c r="A114" t="s">
-        <v>248</v>
-      </c>
-      <c r="B114" t="s">
-        <v>249</v>
-      </c>
-      <c r="C114" t="s">
-        <v>5</v>
-      </c>
-      <c r="D114" s="2">
-        <v>46055.333333333299</v>
-      </c>
-      <c r="E114" s="2">
-        <v>46055.708333333299</v>
-      </c>
-      <c r="F114" t="s">
-        <v>16</v>
-      </c>
-      <c r="G114" s="2">
-        <v>46055.333333333299</v>
-      </c>
-      <c r="H114" s="2">
-        <v>46055.708333333299</v>
-      </c>
-      <c r="I114" t="s">
-        <v>5</v>
-      </c>
-      <c r="J114" t="s">
-        <v>6</v>
-      </c>
-      <c r="K114" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" t="s">
-        <v>250</v>
-      </c>
-      <c r="B115" t="s">
-        <v>251</v>
-      </c>
-      <c r="C115" t="s">
-        <v>5</v>
-      </c>
-      <c r="D115" s="2">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="E115" s="2">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="F115" t="s">
-        <v>16</v>
-      </c>
-      <c r="G115" s="2">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="H115" s="2">
-        <v>46052.333333333299</v>
-      </c>
-      <c r="I115" t="s">
-        <v>5</v>
-      </c>
-      <c r="J115" t="s">
-        <v>6</v>
-      </c>
-      <c r="K115" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" t="s">
-        <v>252</v>
-      </c>
-      <c r="B116" t="s">
-        <v>253</v>
-      </c>
-      <c r="C116" t="s">
-        <v>5</v>
-      </c>
-      <c r="D116" s="2">
-        <v>46051.333333333299</v>
-      </c>
-      <c r="E116" s="2">
-        <v>46051.708333333299</v>
-      </c>
-      <c r="F116" t="s">
-        <v>16</v>
-      </c>
-      <c r="G116" s="2">
-        <v>46051.333333333299</v>
-      </c>
-      <c r="H116" s="2">
-        <v>46051.708333333299</v>
-      </c>
-      <c r="I116" t="s">
-        <v>5</v>
-      </c>
-      <c r="J116" t="s">
-        <v>6</v>
-      </c>
-      <c r="K116" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" t="s">
-        <v>254</v>
-      </c>
-      <c r="B117" t="s">
-        <v>255</v>
-      </c>
-      <c r="C117" t="s">
-        <v>5</v>
-      </c>
-      <c r="D117" s="2">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="E117" s="2">
-        <v>46050.708333333299</v>
-      </c>
-      <c r="F117" t="s">
-        <v>16</v>
-      </c>
-      <c r="G117" s="2">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="H117" s="2">
-        <v>46050.708333333299</v>
-      </c>
-      <c r="I117" t="s">
-        <v>5</v>
-      </c>
-      <c r="J117" t="s">
-        <v>6</v>
-      </c>
-      <c r="K117" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" t="s">
-        <v>256</v>
-      </c>
-      <c r="B118" t="s">
-        <v>257</v>
-      </c>
-      <c r="C118" t="s">
-        <v>5</v>
-      </c>
-      <c r="D118" s="2">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="E118" s="2">
-        <v>46052.708333333299</v>
-      </c>
-      <c r="F118" t="s">
-        <v>16</v>
-      </c>
-      <c r="G118" s="2">
-        <v>46050.333333333299</v>
-      </c>
-      <c r="H118" s="2">
-        <v>46052.708333333299</v>
-      </c>
-      <c r="I118" t="s">
-        <v>5</v>
-      </c>
-      <c r="J118" t="s">
-        <v>6</v>
-      </c>
-      <c r="K118" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" t="s">
-        <v>258</v>
-      </c>
-      <c r="B119" t="s">
-        <v>259</v>
-      </c>
-      <c r="C119" t="s">
-        <v>5</v>
-      </c>
-      <c r="D119" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="E119" s="2">
-        <v>46049.708333333299</v>
-      </c>
-      <c r="F119" t="s">
-        <v>16</v>
-      </c>
-      <c r="G119" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H119" s="2">
-        <v>46049.708333333299</v>
-      </c>
-      <c r="I119" t="s">
-        <v>5</v>
-      </c>
-      <c r="J119" t="s">
-        <v>6</v>
-      </c>
-      <c r="K119" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" t="s">
-        <v>260</v>
-      </c>
-      <c r="B120" t="s">
-        <v>261</v>
-      </c>
-      <c r="C120" t="s">
-        <v>5</v>
-      </c>
-      <c r="D120" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="E120" s="2">
-        <v>46052.708333333299</v>
-      </c>
-      <c r="F120" t="s">
-        <v>16</v>
-      </c>
-      <c r="G120" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H120" s="2">
-        <v>46052.708333333299</v>
-      </c>
-      <c r="I120" t="s">
-        <v>5</v>
-      </c>
-      <c r="J120" t="s">
-        <v>6</v>
-      </c>
-      <c r="K120" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" t="s">
-        <v>262</v>
-      </c>
-      <c r="B121" t="s">
-        <v>263</v>
-      </c>
-      <c r="C121" t="s">
-        <v>5</v>
-      </c>
-      <c r="D121" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="E121" s="2">
-        <v>46048.708333333299</v>
-      </c>
-      <c r="F121" t="s">
-        <v>16</v>
-      </c>
-      <c r="G121" s="2">
-        <v>46048.333333333299</v>
-      </c>
-      <c r="H121" s="2">
-        <v>46048.708333333299</v>
-      </c>
-      <c r="I121" t="s">
-        <v>5</v>
-      </c>
-      <c r="J121" t="s">
-        <v>6</v>
-      </c>
-      <c r="K121" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
-      <c r="A122" t="s">
-        <v>264</v>
-      </c>
-      <c r="B122" t="s">
-        <v>265</v>
-      </c>
-      <c r="C122" t="s">
-        <v>5</v>
-      </c>
-      <c r="D122" s="2">
-        <v>46045.333333333299</v>
-      </c>
-      <c r="E122" s="2">
-        <v>46045.708333333299</v>
-      </c>
-      <c r="F122" t="s">
-        <v>16</v>
-      </c>
-      <c r="G122" s="2">
-        <v>46045.333333333299</v>
-      </c>
-      <c r="H122" s="2">
-        <v>46045.708333333299</v>
-      </c>
-      <c r="I122" t="s">
-        <v>5</v>
-      </c>
-      <c r="J122" t="s">
-        <v>6</v>
-      </c>
-      <c r="K122" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" t="s">
-        <v>266</v>
-      </c>
-      <c r="B123" t="s">
-        <v>267</v>
-      </c>
-      <c r="C123" t="s">
-        <v>5</v>
-      </c>
-      <c r="D123" s="2">
-        <v>46044.333333333299</v>
-      </c>
-      <c r="E123" s="2">
-        <v>46044.708333333299</v>
-      </c>
-      <c r="F123" t="s">
-        <v>16</v>
-      </c>
-      <c r="G123" s="2">
-        <v>46044.333333333299</v>
-      </c>
-      <c r="H123" s="2">
-        <v>46044.708333333299</v>
-      </c>
-      <c r="I123" t="s">
-        <v>5</v>
-      </c>
-      <c r="J123" t="s">
-        <v>6</v>
-      </c>
-      <c r="K123" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
-      <c r="A124" t="s">
-        <v>268</v>
-      </c>
-      <c r="B124" t="s">
-        <v>269</v>
-      </c>
-      <c r="C124" t="s">
-        <v>5</v>
-      </c>
-      <c r="D124" s="2">
-        <v>46043.333333333299</v>
-      </c>
-      <c r="E124" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="F124" t="s">
-        <v>16</v>
-      </c>
-      <c r="G124" s="2">
-        <v>46043.333333333299</v>
-      </c>
-      <c r="H124" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="I124" t="s">
-        <v>5</v>
-      </c>
-      <c r="J124" t="s">
-        <v>6</v>
-      </c>
-      <c r="K124" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" t="s">
-        <v>270</v>
-      </c>
-      <c r="B125" t="s">
-        <v>271</v>
-      </c>
-      <c r="C125" t="s">
-        <v>5</v>
-      </c>
-      <c r="D125" s="2">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="E125" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="F125" t="s">
-        <v>16</v>
-      </c>
-      <c r="G125" s="2">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="H125" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="I125" t="s">
-        <v>5</v>
-      </c>
-      <c r="J125" t="s">
-        <v>6</v>
-      </c>
-      <c r="K125" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" t="s">
-        <v>272</v>
-      </c>
-      <c r="B126" t="s">
-        <v>273</v>
-      </c>
-      <c r="C126" t="s">
-        <v>5</v>
-      </c>
-      <c r="D126" s="2">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="E126" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="F126" t="s">
-        <v>16</v>
-      </c>
-      <c r="G126" s="2">
-        <v>46042.333333333299</v>
-      </c>
-      <c r="H126" s="2">
-        <v>46043.708333333299</v>
-      </c>
-      <c r="I126" t="s">
-        <v>5</v>
-      </c>
-      <c r="J126" t="s">
-        <v>6</v>
-      </c>
-      <c r="K126" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
-      <c r="A127" t="s">
-        <v>274</v>
-      </c>
-      <c r="B127" t="s">
-        <v>275</v>
-      </c>
-      <c r="C127" t="s">
-        <v>5</v>
-      </c>
-      <c r="D127" s="2">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="E127" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="F127" t="s">
-        <v>16</v>
-      </c>
-      <c r="G127" s="2">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="H127" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="I127" t="s">
-        <v>5</v>
-      </c>
-      <c r="J127" t="s">
-        <v>6</v>
-      </c>
-      <c r="K127" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
-      <c r="A128" t="s">
-        <v>276</v>
-      </c>
-      <c r="B128" t="s">
-        <v>277</v>
-      </c>
-      <c r="C128" t="s">
-        <v>5</v>
-      </c>
-      <c r="D128" s="2">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="E128" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="F128" t="s">
-        <v>16</v>
-      </c>
-      <c r="G128" s="2">
-        <v>46041.333333333299</v>
-      </c>
-      <c r="H128" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="I128" t="s">
-        <v>5</v>
-      </c>
-      <c r="J128" t="s">
-        <v>6</v>
-      </c>
-      <c r="K128" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
-      <c r="A129" t="s">
-        <v>278</v>
-      </c>
-      <c r="B129" t="s">
-        <v>279</v>
-      </c>
-      <c r="C129" t="s">
-        <v>5</v>
-      </c>
-      <c r="D129" s="2">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="E129" s="2">
-        <v>46038.708333333299</v>
-      </c>
-      <c r="F129" t="s">
-        <v>16</v>
-      </c>
-      <c r="G129" s="2">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="H129" s="2">
-        <v>46038.708333333299</v>
-      </c>
-      <c r="I129" t="s">
-        <v>5</v>
-      </c>
-      <c r="J129" t="s">
-        <v>6</v>
-      </c>
-      <c r="K129" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" t="s">
-        <v>280</v>
-      </c>
-      <c r="B130" t="s">
-        <v>281</v>
-      </c>
-      <c r="C130" t="s">
-        <v>5</v>
-      </c>
-      <c r="D130" s="2">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="E130" s="2">
-        <v>46038.708333333299</v>
-      </c>
-      <c r="F130" t="s">
-        <v>16</v>
-      </c>
-      <c r="G130" s="2">
-        <v>46038.333333333299</v>
-      </c>
-      <c r="H130" s="2">
-        <v>46038.708333333299</v>
-      </c>
-      <c r="I130" t="s">
-        <v>5</v>
-      </c>
-      <c r="J130" t="s">
-        <v>6</v>
-      </c>
-      <c r="K130" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
-      <c r="A131" t="s">
-        <v>282</v>
-      </c>
-      <c r="B131" t="s">
-        <v>283</v>
-      </c>
-      <c r="C131" t="s">
-        <v>5</v>
-      </c>
-      <c r="D131" s="2">
-        <v>46036.333333333299</v>
-      </c>
-      <c r="E131" s="2">
-        <v>46036.708333333299</v>
-      </c>
-      <c r="F131" t="s">
-        <v>16</v>
-      </c>
-      <c r="G131" s="2">
-        <v>46036.333333333299</v>
-      </c>
-      <c r="H131" s="2">
-        <v>46036.708333333299</v>
-      </c>
-      <c r="I131" t="s">
-        <v>5</v>
-      </c>
-      <c r="J131" t="s">
-        <v>6</v>
-      </c>
-      <c r="K131" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
-      <c r="A132" t="s">
-        <v>284</v>
-      </c>
-      <c r="B132" t="s">
-        <v>285</v>
-      </c>
-      <c r="C132" t="s">
-        <v>5</v>
-      </c>
-      <c r="D132" s="2">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="E132" s="2">
-        <v>46036.708333333299</v>
-      </c>
-      <c r="F132" t="s">
-        <v>16</v>
-      </c>
-      <c r="G132" s="2">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="H132" s="2">
-        <v>46036.708333333299</v>
-      </c>
-      <c r="I132" t="s">
-        <v>5</v>
-      </c>
-      <c r="J132" t="s">
-        <v>6</v>
-      </c>
-      <c r="K132" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
-      <c r="A133" t="s">
-        <v>286</v>
-      </c>
-      <c r="B133" t="s">
-        <v>287</v>
-      </c>
-      <c r="C133" t="s">
-        <v>5</v>
-      </c>
-      <c r="D133" s="2">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="E133" s="2">
-        <v>46035.708333333299</v>
-      </c>
-      <c r="F133" t="s">
-        <v>16</v>
-      </c>
-      <c r="G133" s="2">
-        <v>46035.333333333299</v>
-      </c>
-      <c r="H133" s="2">
-        <v>46035.708333333299</v>
-      </c>
-      <c r="I133" t="s">
-        <v>5</v>
-      </c>
-      <c r="J133" t="s">
-        <v>6</v>
-      </c>
-      <c r="K133" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
-      <c r="A134" t="s">
-        <v>288</v>
-      </c>
-      <c r="B134" t="s">
-        <v>289</v>
-      </c>
-      <c r="C134" t="s">
-        <v>5</v>
-      </c>
-      <c r="D134" s="2">
-        <v>46034.333333333299</v>
-      </c>
-      <c r="E134" s="2">
-        <v>46034.708333333299</v>
-      </c>
-      <c r="F134" t="s">
-        <v>16</v>
-      </c>
-      <c r="G134" s="2">
-        <v>46034.333333333299</v>
-      </c>
-      <c r="H134" s="2">
-        <v>46034.708333333299</v>
-      </c>
-      <c r="I134" t="s">
-        <v>5</v>
-      </c>
-      <c r="J134" t="s">
-        <v>6</v>
-      </c>
-      <c r="K134" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
-      <c r="A135" t="s">
-        <v>290</v>
-      </c>
-      <c r="B135" t="s">
-        <v>291</v>
-      </c>
-      <c r="C135" t="s">
-        <v>5</v>
-      </c>
-      <c r="D135" s="2">
-        <v>46031.333333333299</v>
-      </c>
-      <c r="E135" s="2">
-        <v>46031.708333333299</v>
-      </c>
-      <c r="F135" t="s">
-        <v>16</v>
-      </c>
-      <c r="G135" s="2">
-        <v>46031.333333333299</v>
-      </c>
-      <c r="H135" s="2">
-        <v>46031.708333333299</v>
-      </c>
-      <c r="I135" t="s">
-        <v>5</v>
-      </c>
-      <c r="J135" t="s">
-        <v>6</v>
-      </c>
-      <c r="K135" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11">
-      <c r="A136" t="s">
-        <v>292</v>
-      </c>
-      <c r="B136" t="s">
-        <v>110</v>
-      </c>
-      <c r="C136" t="s">
-        <v>5</v>
-      </c>
-      <c r="D136" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E136" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="F136" t="s">
-        <v>16</v>
-      </c>
-      <c r="G136" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H136" s="2">
-        <v>46041.708333333299</v>
-      </c>
-      <c r="I136" t="s">
-        <v>5</v>
-      </c>
-      <c r="J136" t="s">
-        <v>6</v>
-      </c>
-      <c r="K136" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
-      <c r="A137" t="s">
-        <v>293</v>
-      </c>
-      <c r="B137" t="s">
-        <v>294</v>
-      </c>
-      <c r="C137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D137" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E137" s="2">
-        <v>46030.708333333299</v>
-      </c>
-      <c r="F137" t="s">
-        <v>16</v>
-      </c>
-      <c r="G137" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H137" s="2">
-        <v>46030.708333333299</v>
-      </c>
-      <c r="I137" t="s">
-        <v>5</v>
-      </c>
-      <c r="J137" t="s">
-        <v>6</v>
-      </c>
-      <c r="K137" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11">
-      <c r="A138" t="s">
-        <v>295</v>
-      </c>
-      <c r="B138" t="s">
-        <v>185</v>
-      </c>
-      <c r="C138" t="s">
-        <v>5</v>
-      </c>
-      <c r="D138" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F138" t="s">
-        <v>16</v>
-      </c>
-      <c r="G138" s="2">
-        <v>46029.333333333299</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I138" t="s">
-        <v>5</v>
-      </c>
-      <c r="J138" t="s">
-        <v>6</v>
-      </c>
-      <c r="K138" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11">
-      <c r="A139" t="s">
-        <v>296</v>
-      </c>
-      <c r="B139" t="s">
-        <v>297</v>
-      </c>
-      <c r="C139" t="s">
-        <v>5</v>
-      </c>
-      <c r="D139" s="2">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="E139" s="2">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="F139" t="s">
-        <v>16</v>
-      </c>
-      <c r="G139" s="2">
-        <v>45947.333333333299</v>
-      </c>
-      <c r="H139" s="2">
-        <v>45980.708333333299</v>
-      </c>
-      <c r="I139" t="s">
-        <v>5</v>
-      </c>
-      <c r="J139" t="s">
-        <v>6</v>
-      </c>
-      <c r="K139" t="s">
         <v>6</v>
       </c>
     </row>
@@ -6229,17 +4636,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>298</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
